--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131448361</v>
+        <v>131448402</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>78915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386782</v>
+        <v>386676</v>
       </c>
       <c r="R2" t="n">
-        <v>6758744</v>
+        <v>6758633</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131448360</v>
+        <v>131448307</v>
       </c>
       <c r="B3" t="n">
-        <v>79273</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386785</v>
+        <v>386416</v>
       </c>
       <c r="R3" t="n">
-        <v>6758750</v>
+        <v>6758577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448307</v>
+        <v>131448361</v>
       </c>
       <c r="B5" t="n">
         <v>79249</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386416</v>
+        <v>386782</v>
       </c>
       <c r="R5" t="n">
-        <v>6758577</v>
+        <v>6758744</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448402</v>
+        <v>131448360</v>
       </c>
       <c r="B6" t="n">
-        <v>78915</v>
+        <v>79273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386676</v>
+        <v>386785</v>
       </c>
       <c r="R6" t="n">
-        <v>6758633</v>
+        <v>6758750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131448324</v>
+        <v>131448387</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>78915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386405</v>
+        <v>386707</v>
       </c>
       <c r="R8" t="n">
-        <v>6758668</v>
+        <v>6758689</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,48 +1422,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131448406</v>
+        <v>131440197</v>
       </c>
       <c r="B9" t="n">
-        <v>79868</v>
+        <v>79273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386719</v>
+        <v>386393</v>
       </c>
       <c r="R9" t="n">
-        <v>6758587</v>
+        <v>6758564</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,71 +1490,62 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131448356</v>
+        <v>131448406</v>
       </c>
       <c r="B10" t="n">
-        <v>79273</v>
+        <v>79868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386780</v>
+        <v>386719</v>
       </c>
       <c r="R10" t="n">
-        <v>6758712</v>
+        <v>6758587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1590,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1609,7 +1600,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,32 +1627,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131448387</v>
+        <v>131448356</v>
       </c>
       <c r="B11" t="n">
-        <v>78915</v>
+        <v>79273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1671,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386707</v>
+        <v>386780</v>
       </c>
       <c r="R11" t="n">
-        <v>6758689</v>
+        <v>6758712</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,7 +1697,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1716,7 +1707,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131448319</v>
+        <v>131440187</v>
       </c>
       <c r="B12" t="n">
         <v>57076</v>
@@ -1772,24 +1763,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386383</v>
+        <v>386361</v>
       </c>
       <c r="R12" t="n">
-        <v>6758654</v>
+        <v>6758535</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1816,19 +1810,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1843,57 +1827,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131440221</v>
+        <v>131440186</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386525</v>
+        <v>386354</v>
       </c>
       <c r="R13" t="n">
-        <v>6758695</v>
+        <v>6758536</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1952,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131440186</v>
+        <v>131448319</v>
       </c>
       <c r="B14" t="n">
         <v>57076</v>
@@ -1981,27 +1973,24 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386354</v>
+        <v>386383</v>
       </c>
       <c r="R14" t="n">
-        <v>6758536</v>
+        <v>6758654</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2028,9 +2017,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2045,68 +2044,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131440187</v>
+        <v>131448324</v>
       </c>
       <c r="B15" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386361</v>
+        <v>386405</v>
       </c>
       <c r="R15" t="n">
-        <v>6758535</v>
+        <v>6758668</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2133,9 +2124,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2150,44 +2151,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131440197</v>
+        <v>131440221</v>
       </c>
       <c r="B16" t="n">
-        <v>79273</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386393</v>
+        <v>386525</v>
       </c>
       <c r="R16" t="n">
-        <v>6758564</v>
+        <v>6758695</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2241,7 +2242,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131448350</v>
+        <v>131448344</v>
       </c>
       <c r="B18" t="n">
-        <v>79007</v>
+        <v>78915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386644</v>
+        <v>386506</v>
       </c>
       <c r="R18" t="n">
-        <v>6758591</v>
+        <v>6758691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448344</v>
+        <v>131448363</v>
       </c>
       <c r="B19" t="n">
         <v>78915</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386506</v>
+        <v>386784</v>
       </c>
       <c r="R19" t="n">
-        <v>6758691</v>
+        <v>6758735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448370</v>
+        <v>131448379</v>
       </c>
       <c r="B20" t="n">
-        <v>79839</v>
+        <v>78915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386751</v>
+        <v>386696</v>
       </c>
       <c r="R20" t="n">
-        <v>6758793</v>
+        <v>6758781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448299</v>
+        <v>131440220</v>
       </c>
       <c r="B21" t="n">
         <v>79249</v>
@@ -2719,17 +2719,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386440</v>
+        <v>386519</v>
       </c>
       <c r="R21" t="n">
-        <v>6758599</v>
+        <v>6758698</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2756,19 +2756,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2783,22 +2773,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131448363</v>
+        <v>131448295</v>
       </c>
       <c r="B22" t="n">
-        <v>78915</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386784</v>
+        <v>386474</v>
       </c>
       <c r="R22" t="n">
-        <v>6758735</v>
+        <v>6758587</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2855,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2875,7 +2865,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2892,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131448295</v>
+        <v>131448375</v>
       </c>
       <c r="B23" t="n">
         <v>79249</v>
@@ -2937,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386474</v>
+        <v>386743</v>
       </c>
       <c r="R23" t="n">
-        <v>6758587</v>
+        <v>6758789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2982,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448379</v>
+        <v>131448299</v>
       </c>
       <c r="B24" t="n">
-        <v>78915</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3020,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3044,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386696</v>
+        <v>386440</v>
       </c>
       <c r="R24" t="n">
-        <v>6758781</v>
+        <v>6758599</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3089,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448375</v>
+        <v>131448370</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,21 +3117,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3151,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386743</v>
+        <v>386751</v>
       </c>
       <c r="R25" t="n">
-        <v>6758789</v>
+        <v>6758793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3186,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3196,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3223,56 +3213,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131440191</v>
+        <v>131448350</v>
       </c>
       <c r="B26" t="n">
-        <v>57076</v>
+        <v>79007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386397</v>
+        <v>386644</v>
       </c>
       <c r="R26" t="n">
-        <v>6758574</v>
+        <v>6758591</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3299,9 +3281,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3316,57 +3308,65 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131440220</v>
+        <v>131440191</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386519</v>
+        <v>386397</v>
       </c>
       <c r="R27" t="n">
-        <v>6758698</v>
+        <v>6758574</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448368</v>
+        <v>131448292</v>
       </c>
       <c r="B28" t="n">
         <v>79249</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386787</v>
+        <v>386495</v>
       </c>
       <c r="R28" t="n">
-        <v>6758812</v>
+        <v>6758597</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448292</v>
+        <v>131448368</v>
       </c>
       <c r="B29" t="n">
         <v>79249</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386495</v>
+        <v>386787</v>
       </c>
       <c r="R29" t="n">
-        <v>6758597</v>
+        <v>6758812</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,7 +3746,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448327</v>
+        <v>131448386</v>
       </c>
       <c r="B31" t="n">
         <v>79249</v>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386449</v>
+        <v>386697</v>
       </c>
       <c r="R31" t="n">
-        <v>6758648</v>
+        <v>6758686</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,7 +3853,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448386</v>
+        <v>131448329</v>
       </c>
       <c r="B32" t="n">
         <v>79249</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386697</v>
+        <v>386494</v>
       </c>
       <c r="R32" t="n">
-        <v>6758686</v>
+        <v>6758631</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,7 +3960,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448329</v>
+        <v>131448327</v>
       </c>
       <c r="B33" t="n">
         <v>79249</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386494</v>
+        <v>386449</v>
       </c>
       <c r="R33" t="n">
-        <v>6758631</v>
+        <v>6758648</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4174,7 +4174,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448382</v>
+        <v>131440215</v>
       </c>
       <c r="B35" t="n">
         <v>79249</v>
@@ -4205,17 +4205,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386718</v>
+        <v>386402</v>
       </c>
       <c r="R35" t="n">
-        <v>6758734</v>
+        <v>6758574</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,19 +4242,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,68 +4259,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131440192</v>
+        <v>131448382</v>
       </c>
       <c r="B36" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386414</v>
+        <v>386718</v>
       </c>
       <c r="R36" t="n">
-        <v>6758608</v>
+        <v>6758734</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4357,9 +4339,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4374,57 +4366,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131440215</v>
+        <v>131440192</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386402</v>
+        <v>386414</v>
       </c>
       <c r="R37" t="n">
-        <v>6758574</v>
+        <v>6758608</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131448403</v>
+        <v>131448339</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>78915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386650</v>
+        <v>386506</v>
       </c>
       <c r="R43" t="n">
-        <v>6758630</v>
+        <v>6758684</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5130,10 +5130,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448369</v>
+        <v>131440171</v>
       </c>
       <c r="B44" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5141,37 +5141,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386774</v>
+        <v>386519</v>
       </c>
       <c r="R44" t="n">
-        <v>6758809</v>
+        <v>6758682</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5198,19 +5198,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5225,22 +5215,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448339</v>
+        <v>131448346</v>
       </c>
       <c r="B45" t="n">
-        <v>78915</v>
+        <v>79868</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5248,21 +5238,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5272,10 +5262,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386506</v>
+        <v>386558</v>
       </c>
       <c r="R45" t="n">
-        <v>6758684</v>
+        <v>6758731</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5307,7 +5297,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5317,7 +5307,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5344,48 +5334,56 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131448322</v>
+        <v>131440180</v>
       </c>
       <c r="B46" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386380</v>
+        <v>386351</v>
       </c>
       <c r="R46" t="n">
-        <v>6758666</v>
+        <v>6758581</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5412,19 +5410,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5439,19 +5427,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448289</v>
+        <v>131448403</v>
       </c>
       <c r="B47" t="n">
         <v>79249</v>
@@ -5486,10 +5474,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386519</v>
+        <v>386650</v>
       </c>
       <c r="R47" t="n">
-        <v>6758591</v>
+        <v>6758630</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5521,7 +5509,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5531,7 +5519,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5558,10 +5546,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131448346</v>
+        <v>131448289</v>
       </c>
       <c r="B48" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5569,21 +5557,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5593,10 +5581,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386558</v>
+        <v>386519</v>
       </c>
       <c r="R48" t="n">
-        <v>6758731</v>
+        <v>6758591</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,7 +5616,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5638,7 +5626,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5665,56 +5653,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131440180</v>
+        <v>131448369</v>
       </c>
       <c r="B49" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386351</v>
+        <v>386774</v>
       </c>
       <c r="R49" t="n">
-        <v>6758581</v>
+        <v>6758809</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5741,9 +5721,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5758,22 +5748,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131440171</v>
+        <v>131448322</v>
       </c>
       <c r="B50" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5781,37 +5771,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386519</v>
+        <v>386380</v>
       </c>
       <c r="R50" t="n">
-        <v>6758682</v>
+        <v>6758666</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5838,9 +5828,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5855,12 +5855,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5974,10 +5974,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131448384</v>
+        <v>131440169</v>
       </c>
       <c r="B52" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5985,37 +5985,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386721</v>
+        <v>386434</v>
       </c>
       <c r="R52" t="n">
-        <v>6758722</v>
+        <v>6758668</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6042,19 +6042,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6069,22 +6059,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131440169</v>
+        <v>131448365</v>
       </c>
       <c r="B53" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6092,37 +6082,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386434</v>
+        <v>386808</v>
       </c>
       <c r="R53" t="n">
-        <v>6758668</v>
+        <v>6758791</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6149,9 +6139,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6166,19 +6166,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448365</v>
+        <v>131448297</v>
       </c>
       <c r="B54" t="n">
         <v>79249</v>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386808</v>
+        <v>386455</v>
       </c>
       <c r="R54" t="n">
-        <v>6758791</v>
+        <v>6758589</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6285,7 +6285,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131448297</v>
+        <v>131448330</v>
       </c>
       <c r="B55" t="n">
         <v>79249</v>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386455</v>
+        <v>386474</v>
       </c>
       <c r="R55" t="n">
-        <v>6758589</v>
+        <v>6758628</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6392,50 +6392,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131448364</v>
+        <v>131448384</v>
       </c>
       <c r="B56" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386784</v>
+        <v>386721</v>
       </c>
       <c r="R56" t="n">
-        <v>6758773</v>
+        <v>6758722</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6467,7 +6462,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6477,7 +6472,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6504,45 +6499,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131448330</v>
+        <v>131448364</v>
       </c>
       <c r="B57" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386474</v>
+        <v>386784</v>
       </c>
       <c r="R57" t="n">
-        <v>6758628</v>
+        <v>6758773</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131448312</v>
+        <v>131448293</v>
       </c>
       <c r="B58" t="n">
-        <v>79868</v>
+        <v>78915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386410</v>
+        <v>386508</v>
       </c>
       <c r="R58" t="n">
-        <v>6758596</v>
+        <v>6758593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6718,7 +6718,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131448293</v>
+        <v>131448286</v>
       </c>
       <c r="B59" t="n">
         <v>78915</v>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386508</v>
+        <v>386475</v>
       </c>
       <c r="R59" t="n">
-        <v>6758593</v>
+        <v>6758559</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6825,50 +6825,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131448283</v>
+        <v>131448312</v>
       </c>
       <c r="B60" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>386456</v>
+        <v>386410</v>
       </c>
       <c r="R60" t="n">
-        <v>6758560</v>
+        <v>6758596</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6900,7 +6895,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6910,7 +6905,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6937,45 +6932,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131448338</v>
+        <v>131448283</v>
       </c>
       <c r="B61" t="n">
-        <v>79007</v>
+        <v>57076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>386506</v>
+        <v>386456</v>
       </c>
       <c r="R61" t="n">
-        <v>6758684</v>
+        <v>6758560</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7044,48 +7044,56 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131448286</v>
+        <v>131440181</v>
       </c>
       <c r="B62" t="n">
-        <v>78915</v>
+        <v>57076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386475</v>
+        <v>386339</v>
       </c>
       <c r="R62" t="n">
         <v>6758559</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7112,19 +7120,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7139,68 +7137,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131440181</v>
+        <v>131448338</v>
       </c>
       <c r="B63" t="n">
-        <v>57076</v>
+        <v>79007</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>386339</v>
+        <v>386506</v>
       </c>
       <c r="R63" t="n">
-        <v>6758559</v>
+        <v>6758684</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7227,9 +7217,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7244,22 +7244,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131448404</v>
+        <v>131448291</v>
       </c>
       <c r="B64" t="n">
-        <v>79249</v>
+        <v>78915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7267,21 +7267,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>386684</v>
+        <v>386519</v>
       </c>
       <c r="R64" t="n">
-        <v>6758614</v>
+        <v>6758587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7363,10 +7363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131448318</v>
+        <v>131440166</v>
       </c>
       <c r="B65" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7374,37 +7374,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>386391</v>
+        <v>386386</v>
       </c>
       <c r="R65" t="n">
-        <v>6758637</v>
+        <v>6758567</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7431,19 +7431,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7458,62 +7448,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131448311</v>
+        <v>131448381</v>
       </c>
       <c r="B66" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386418</v>
+        <v>386711</v>
       </c>
       <c r="R66" t="n">
-        <v>6758590</v>
+        <v>6758768</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7545,7 +7530,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7555,7 +7540,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7582,48 +7567,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131448381</v>
+        <v>131440204</v>
       </c>
       <c r="B67" t="n">
-        <v>79249</v>
+        <v>79273</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386711</v>
+        <v>386401</v>
       </c>
       <c r="R67" t="n">
-        <v>6758768</v>
+        <v>6758592</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7650,19 +7635,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7677,22 +7652,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131448323</v>
+        <v>131448281</v>
       </c>
       <c r="B68" t="n">
-        <v>79249</v>
+        <v>79006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7700,21 +7675,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7724,10 +7699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386418</v>
+        <v>386443</v>
       </c>
       <c r="R68" t="n">
-        <v>6758667</v>
+        <v>6758546</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7759,7 +7734,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7769,7 +7744,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7796,45 +7771,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131448366</v>
+        <v>131448311</v>
       </c>
       <c r="B69" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>386800</v>
+        <v>386418</v>
       </c>
       <c r="R69" t="n">
-        <v>6758785</v>
+        <v>6758590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7866,7 +7846,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7876,7 +7856,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7903,48 +7883,56 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131448291</v>
+        <v>131440185</v>
       </c>
       <c r="B70" t="n">
-        <v>78915</v>
+        <v>57076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386519</v>
+        <v>386353</v>
       </c>
       <c r="R70" t="n">
-        <v>6758587</v>
+        <v>6758548</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7971,19 +7959,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7998,60 +7976,68 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131448281</v>
+        <v>131440179</v>
       </c>
       <c r="B71" t="n">
-        <v>79006</v>
+        <v>57076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386443</v>
+        <v>386369</v>
       </c>
       <c r="R71" t="n">
-        <v>6758546</v>
+        <v>6758575</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8078,19 +8064,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:39</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8105,68 +8081,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131440185</v>
+        <v>131448404</v>
       </c>
       <c r="B72" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386353</v>
+        <v>386684</v>
       </c>
       <c r="R72" t="n">
-        <v>6758548</v>
+        <v>6758614</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8193,9 +8161,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8210,68 +8188,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131440179</v>
+        <v>131448323</v>
       </c>
       <c r="B73" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>386369</v>
+        <v>386418</v>
       </c>
       <c r="R73" t="n">
-        <v>6758575</v>
+        <v>6758667</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8298,9 +8268,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8315,60 +8295,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131440204</v>
+        <v>131448366</v>
       </c>
       <c r="B74" t="n">
-        <v>79273</v>
+        <v>79249</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386401</v>
+        <v>386800</v>
       </c>
       <c r="R74" t="n">
-        <v>6758592</v>
+        <v>6758785</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8395,9 +8375,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8412,22 +8402,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131440166</v>
+        <v>131448318</v>
       </c>
       <c r="B75" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8435,37 +8425,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386386</v>
+        <v>386391</v>
       </c>
       <c r="R75" t="n">
-        <v>6758567</v>
+        <v>6758637</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8492,9 +8482,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8509,22 +8509,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131448280</v>
+        <v>131448372</v>
       </c>
       <c r="B76" t="n">
-        <v>79007</v>
+        <v>79249</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8532,21 +8532,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8556,10 +8556,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>386443</v>
+        <v>386764</v>
       </c>
       <c r="R76" t="n">
-        <v>6758546</v>
+        <v>6758806</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8628,7 +8628,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131448317</v>
+        <v>131440152</v>
       </c>
       <c r="B77" t="n">
         <v>79868</v>
@@ -8659,17 +8659,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386389</v>
+        <v>386484</v>
       </c>
       <c r="R77" t="n">
-        <v>6758642</v>
+        <v>6758687</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8696,49 +8696,40 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131448372</v>
+        <v>131448317</v>
       </c>
       <c r="B78" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8746,21 +8737,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8770,10 +8761,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>386764</v>
+        <v>386389</v>
       </c>
       <c r="R78" t="n">
-        <v>6758806</v>
+        <v>6758642</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8805,7 +8796,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8815,7 +8806,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8939,10 +8930,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131440152</v>
+        <v>131448280</v>
       </c>
       <c r="B80" t="n">
-        <v>79868</v>
+        <v>79007</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8950,37 +8941,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>386484</v>
+        <v>386443</v>
       </c>
       <c r="R80" t="n">
-        <v>6758687</v>
+        <v>6758546</v>
       </c>
       <c r="S80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9007,80 +8998,84 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131448314</v>
+        <v>131448341</v>
       </c>
       <c r="B81" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>386402</v>
+        <v>386504</v>
       </c>
       <c r="R81" t="n">
-        <v>6758596</v>
+        <v>6758683</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9112,7 +9107,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9122,7 +9117,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9149,45 +9144,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131448341</v>
+        <v>131448314</v>
       </c>
       <c r="B82" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>386504</v>
+        <v>386402</v>
       </c>
       <c r="R82" t="n">
-        <v>6758683</v>
+        <v>6758596</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9256,7 +9256,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131448315</v>
+        <v>131448343</v>
       </c>
       <c r="B83" t="n">
         <v>79249</v>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>386402</v>
+        <v>386512</v>
       </c>
       <c r="R83" t="n">
-        <v>6758596</v>
+        <v>6758697</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9363,32 +9363,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131448367</v>
+        <v>131448362</v>
       </c>
       <c r="B84" t="n">
-        <v>79273</v>
+        <v>79249</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9398,10 +9398,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>386774</v>
+        <v>386784</v>
       </c>
       <c r="R84" t="n">
-        <v>6758809</v>
+        <v>6758735</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9470,7 +9470,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131448343</v>
+        <v>131448315</v>
       </c>
       <c r="B85" t="n">
         <v>79249</v>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>386512</v>
+        <v>386402</v>
       </c>
       <c r="R85" t="n">
-        <v>6758697</v>
+        <v>6758596</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9577,32 +9577,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131448362</v>
+        <v>131448367</v>
       </c>
       <c r="B86" t="n">
-        <v>79249</v>
+        <v>79273</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>386784</v>
+        <v>386774</v>
       </c>
       <c r="R86" t="n">
-        <v>6758735</v>
+        <v>6758809</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9684,10 +9684,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131448285</v>
+        <v>131440172</v>
       </c>
       <c r="B87" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9695,37 +9695,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>386496</v>
+        <v>386524</v>
       </c>
       <c r="R87" t="n">
-        <v>6758565</v>
+        <v>6758661</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9752,19 +9752,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9779,60 +9769,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131448359</v>
+        <v>131440205</v>
       </c>
       <c r="B88" t="n">
-        <v>79868</v>
+        <v>79273</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>386785</v>
+        <v>386413</v>
       </c>
       <c r="R88" t="n">
-        <v>6758750</v>
+        <v>6758608</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9859,19 +9849,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9886,22 +9866,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131440172</v>
+        <v>131448285</v>
       </c>
       <c r="B89" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9909,37 +9889,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>386524</v>
+        <v>386496</v>
       </c>
       <c r="R89" t="n">
-        <v>6758661</v>
+        <v>6758565</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9966,9 +9946,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9983,68 +9973,60 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131440190</v>
+        <v>131448359</v>
       </c>
       <c r="B90" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>386402</v>
+        <v>386785</v>
       </c>
       <c r="R90" t="n">
-        <v>6758572</v>
+        <v>6758750</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10071,9 +10053,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10088,22 +10080,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131440205</v>
+        <v>131440190</v>
       </c>
       <c r="B91" t="n">
-        <v>79273</v>
+        <v>57076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10111,34 +10103,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>386413</v>
+        <v>386402</v>
       </c>
       <c r="R91" t="n">
-        <v>6758608</v>
+        <v>6758572</v>
       </c>
       <c r="S91" t="n">
         <v>20</v>
@@ -10302,48 +10302,56 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131448351</v>
+        <v>131440189</v>
       </c>
       <c r="B93" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>386637</v>
+        <v>386396</v>
       </c>
       <c r="R93" t="n">
-        <v>6758584</v>
+        <v>6758549</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10370,19 +10378,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10397,19 +10395,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131448380</v>
+        <v>131448351</v>
       </c>
       <c r="B94" t="n">
         <v>79249</v>
@@ -10444,10 +10442,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>386713</v>
+        <v>386637</v>
       </c>
       <c r="R94" t="n">
-        <v>6758747</v>
+        <v>6758584</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10479,7 +10477,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10489,7 +10487,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10516,10 +10514,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131440210</v>
+        <v>131448380</v>
       </c>
       <c r="B95" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10527,37 +10525,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>386347</v>
+        <v>386713</v>
       </c>
       <c r="R95" t="n">
-        <v>6758542</v>
+        <v>6758747</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10584,9 +10582,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10601,65 +10609,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131440189</v>
+        <v>131440210</v>
       </c>
       <c r="B96" t="n">
-        <v>57076</v>
+        <v>79006</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>386396</v>
+        <v>386347</v>
       </c>
       <c r="R96" t="n">
-        <v>6758549</v>
+        <v>6758542</v>
       </c>
       <c r="S96" t="n">
         <v>20</v>
@@ -10718,7 +10718,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131448284</v>
+        <v>131440219</v>
       </c>
       <c r="B97" t="n">
         <v>79249</v>
@@ -10749,17 +10749,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>386456</v>
+        <v>386495</v>
       </c>
       <c r="R97" t="n">
-        <v>6758560</v>
+        <v>6758684</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10786,19 +10786,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10813,12 +10803,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10932,7 +10922,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131448345</v>
+        <v>131440216</v>
       </c>
       <c r="B99" t="n">
         <v>79249</v>
@@ -10963,17 +10953,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>386536</v>
+        <v>386401</v>
       </c>
       <c r="R99" t="n">
-        <v>6758715</v>
+        <v>6758591</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11000,19 +10990,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11027,19 +11007,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131440219</v>
+        <v>131448345</v>
       </c>
       <c r="B100" t="n">
         <v>79249</v>
@@ -11070,17 +11050,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>386495</v>
+        <v>386536</v>
       </c>
       <c r="R100" t="n">
-        <v>6758684</v>
+        <v>6758715</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11107,9 +11087,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11124,19 +11114,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131440216</v>
+        <v>131448284</v>
       </c>
       <c r="B101" t="n">
         <v>79249</v>
@@ -11167,17 +11157,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>386401</v>
+        <v>386456</v>
       </c>
       <c r="R101" t="n">
-        <v>6758591</v>
+        <v>6758560</v>
       </c>
       <c r="S101" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11204,9 +11194,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11221,12 +11221,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131440225</v>
+        <v>131448399</v>
       </c>
       <c r="B104" t="n">
-        <v>78915</v>
+        <v>79249</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11446,37 +11446,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>386426</v>
+        <v>386647</v>
       </c>
       <c r="R104" t="n">
-        <v>6758644</v>
+        <v>6758685</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11503,9 +11503,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11520,19 +11530,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131440217</v>
+        <v>131448304</v>
       </c>
       <c r="B105" t="n">
         <v>79249</v>
@@ -11563,17 +11573,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>386476</v>
+        <v>386423</v>
       </c>
       <c r="R105" t="n">
-        <v>6758669</v>
+        <v>6758618</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11600,9 +11610,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11617,19 +11637,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131448399</v>
+        <v>131448337</v>
       </c>
       <c r="B106" t="n">
         <v>79249</v>
@@ -11664,10 +11684,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>386647</v>
+        <v>386503</v>
       </c>
       <c r="R106" t="n">
-        <v>6758685</v>
+        <v>6758670</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11699,7 +11719,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11709,7 +11729,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11736,7 +11756,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131448304</v>
+        <v>131440217</v>
       </c>
       <c r="B107" t="n">
         <v>79249</v>
@@ -11767,17 +11787,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>386423</v>
+        <v>386476</v>
       </c>
       <c r="R107" t="n">
-        <v>6758618</v>
+        <v>6758669</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11804,19 +11824,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11831,22 +11841,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131448337</v>
+        <v>131440225</v>
       </c>
       <c r="B108" t="n">
-        <v>79249</v>
+        <v>78915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11854,37 +11864,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>386503</v>
+        <v>386426</v>
       </c>
       <c r="R108" t="n">
-        <v>6758670</v>
+        <v>6758644</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11911,19 +11921,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11938,57 +11938,62 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131448401</v>
+        <v>131448303</v>
       </c>
       <c r="B109" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>386677</v>
+        <v>386417</v>
       </c>
       <c r="R109" t="n">
-        <v>6758630</v>
+        <v>6758612</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12020,7 +12025,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12030,7 +12035,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12057,50 +12062,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131448303</v>
+        <v>131448401</v>
       </c>
       <c r="B110" t="n">
-        <v>57076</v>
+        <v>79249</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>386417</v>
+        <v>386677</v>
       </c>
       <c r="R110" t="n">
-        <v>6758612</v>
+        <v>6758630</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12468,10 +12468,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131448308</v>
+        <v>131448335</v>
       </c>
       <c r="B114" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12479,21 +12479,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12503,10 +12503,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>386413</v>
+        <v>386526</v>
       </c>
       <c r="R114" t="n">
-        <v>6758591</v>
+        <v>6758655</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12575,50 +12575,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131448287</v>
+        <v>131448308</v>
       </c>
       <c r="B115" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>386516</v>
+        <v>386413</v>
       </c>
       <c r="R115" t="n">
-        <v>6758592</v>
+        <v>6758591</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12650,7 +12645,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12660,7 +12655,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12687,45 +12682,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131448335</v>
+        <v>131448287</v>
       </c>
       <c r="B116" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>386526</v>
+        <v>386516</v>
       </c>
       <c r="R116" t="n">
-        <v>6758655</v>
+        <v>6758592</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12794,10 +12794,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131440167</v>
+        <v>131448374</v>
       </c>
       <c r="B117" t="n">
-        <v>79868</v>
+        <v>78915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12805,37 +12805,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>386367</v>
+        <v>386764</v>
       </c>
       <c r="R117" t="n">
-        <v>6758574</v>
+        <v>6758806</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12862,9 +12862,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12879,57 +12889,62 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131448374</v>
+        <v>131448268</v>
       </c>
       <c r="B118" t="n">
-        <v>78915</v>
+        <v>57076</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>386764</v>
+        <v>386348</v>
       </c>
       <c r="R118" t="n">
-        <v>6758806</v>
+        <v>6758527</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12961,7 +12976,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12971,7 +12986,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12998,7 +13013,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131448268</v>
+        <v>131448320</v>
       </c>
       <c r="B119" t="n">
         <v>57076</v>
@@ -13038,10 +13053,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>386348</v>
+        <v>386392</v>
       </c>
       <c r="R119" t="n">
-        <v>6758527</v>
+        <v>6758650</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13073,7 +13088,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13083,7 +13098,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13217,53 +13232,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131448320</v>
+        <v>131440167</v>
       </c>
       <c r="B121" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>386392</v>
+        <v>386367</v>
       </c>
       <c r="R121" t="n">
-        <v>6758650</v>
+        <v>6758574</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13290,19 +13300,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13317,12 +13317,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13650,10 +13650,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131448397</v>
+        <v>131448342</v>
       </c>
       <c r="B125" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13661,21 +13661,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13685,10 +13685,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>386638</v>
+        <v>386512</v>
       </c>
       <c r="R125" t="n">
-        <v>6758692</v>
+        <v>6758697</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13757,10 +13757,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131448342</v>
+        <v>131448397</v>
       </c>
       <c r="B126" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13768,21 +13768,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13792,10 +13792,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>386512</v>
+        <v>386638</v>
       </c>
       <c r="R126" t="n">
-        <v>6758697</v>
+        <v>6758692</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448402</v>
       </c>
       <c r="B2" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,55 +775,63 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131448307</v>
+        <v>131440184</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386416</v>
+        <v>386349</v>
       </c>
       <c r="R3" t="n">
-        <v>6758577</v>
+        <v>6758545</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +858,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +875,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448316</v>
+        <v>131448361</v>
       </c>
       <c r="B4" t="n">
-        <v>79273</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386346</v>
+        <v>386782</v>
       </c>
       <c r="R4" t="n">
-        <v>6758614</v>
+        <v>6758744</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +957,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +967,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +994,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448361</v>
+        <v>131448360</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386782</v>
+        <v>386785</v>
       </c>
       <c r="R5" t="n">
-        <v>6758744</v>
+        <v>6758750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448360</v>
+        <v>131448316</v>
       </c>
       <c r="B6" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386785</v>
+        <v>386346</v>
       </c>
       <c r="R6" t="n">
-        <v>6758750</v>
+        <v>6758614</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1171,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1181,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,56 +1208,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131440184</v>
+        <v>131448307</v>
       </c>
       <c r="B7" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386349</v>
+        <v>386416</v>
       </c>
       <c r="R7" t="n">
-        <v>6758545</v>
+        <v>6758577</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1286,9 +1276,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1318,7 +1318,7 @@
         <v>131448387</v>
       </c>
       <c r="B8" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131440197</v>
+        <v>131440187</v>
       </c>
       <c r="B9" t="n">
-        <v>79273</v>
+        <v>57076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,34 +1433,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386393</v>
+        <v>386361</v>
       </c>
       <c r="R9" t="n">
-        <v>6758564</v>
+        <v>6758535</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1501,7 +1509,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1520,48 +1527,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131448406</v>
+        <v>131440186</v>
       </c>
       <c r="B10" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386719</v>
+        <v>386354</v>
       </c>
       <c r="R10" t="n">
-        <v>6758587</v>
+        <v>6758536</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,19 +1603,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,22 +1620,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131448356</v>
+        <v>131448319</v>
       </c>
       <c r="B11" t="n">
-        <v>79273</v>
+        <v>57076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,34 +1643,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386780</v>
+        <v>386383</v>
       </c>
       <c r="R11" t="n">
-        <v>6758712</v>
+        <v>6758654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,7 +1707,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1707,7 +1717,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,56 +1744,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131440187</v>
+        <v>131448324</v>
       </c>
       <c r="B12" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386361</v>
+        <v>386405</v>
       </c>
       <c r="R12" t="n">
-        <v>6758535</v>
+        <v>6758668</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1810,9 +1812,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,22 +1839,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131440186</v>
+        <v>131440197</v>
       </c>
       <c r="B13" t="n">
-        <v>57076</v>
+        <v>79274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,42 +1862,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386354</v>
+        <v>386393</v>
       </c>
       <c r="R13" t="n">
-        <v>6758536</v>
+        <v>6758564</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1926,6 +1930,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1944,50 +1949,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131448319</v>
+        <v>131448406</v>
       </c>
       <c r="B14" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386383</v>
+        <v>386719</v>
       </c>
       <c r="R14" t="n">
-        <v>6758654</v>
+        <v>6758587</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,39 +2049,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131448324</v>
+        <v>131448356</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386405</v>
+        <v>386780</v>
       </c>
       <c r="R15" t="n">
-        <v>6758668</v>
+        <v>6758712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,7 +2166,7 @@
         <v>131440221</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448259</v>
+        <v>131448370</v>
       </c>
       <c r="B17" t="n">
-        <v>78915</v>
+        <v>79840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386484</v>
+        <v>386751</v>
       </c>
       <c r="R17" t="n">
-        <v>6758522</v>
+        <v>6758793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131448344</v>
+        <v>131448259</v>
       </c>
       <c r="B18" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386506</v>
+        <v>386484</v>
       </c>
       <c r="R18" t="n">
-        <v>6758691</v>
+        <v>6758522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448363</v>
+        <v>131448344</v>
       </c>
       <c r="B19" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386784</v>
+        <v>386506</v>
       </c>
       <c r="R19" t="n">
-        <v>6758735</v>
+        <v>6758691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448379</v>
+        <v>131448363</v>
       </c>
       <c r="B20" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386696</v>
+        <v>386784</v>
       </c>
       <c r="R20" t="n">
-        <v>6758781</v>
+        <v>6758735</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131440220</v>
+        <v>131448379</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>78916</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,37 +2699,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386519</v>
+        <v>386696</v>
       </c>
       <c r="R21" t="n">
-        <v>6758698</v>
+        <v>6758781</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2756,9 +2756,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2773,22 +2783,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131448295</v>
+        <v>131440220</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2816,17 +2826,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386474</v>
+        <v>386519</v>
       </c>
       <c r="R22" t="n">
-        <v>6758587</v>
+        <v>6758698</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2853,19 +2863,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2880,22 +2880,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131448375</v>
+        <v>131448299</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386743</v>
+        <v>386440</v>
       </c>
       <c r="R23" t="n">
-        <v>6758789</v>
+        <v>6758599</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448299</v>
+        <v>131448295</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386440</v>
+        <v>386474</v>
       </c>
       <c r="R24" t="n">
-        <v>6758599</v>
+        <v>6758587</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,10 +3106,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448370</v>
+        <v>131448375</v>
       </c>
       <c r="B25" t="n">
-        <v>79839</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,21 +3117,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386751</v>
+        <v>386743</v>
       </c>
       <c r="R25" t="n">
-        <v>6758793</v>
+        <v>6758789</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,48 +3213,56 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448350</v>
+        <v>131440191</v>
       </c>
       <c r="B26" t="n">
-        <v>79007</v>
+        <v>57076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386644</v>
+        <v>386397</v>
       </c>
       <c r="R26" t="n">
-        <v>6758591</v>
+        <v>6758574</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3281,19 +3289,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3308,68 +3306,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131440191</v>
+        <v>131448350</v>
       </c>
       <c r="B27" t="n">
-        <v>57076</v>
+        <v>79008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386397</v>
+        <v>386644</v>
       </c>
       <c r="R27" t="n">
-        <v>6758574</v>
+        <v>6758591</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3396,9 +3386,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3413,12 +3413,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3428,7 +3428,7 @@
         <v>131448292</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>131448368</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>131448409</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448386</v>
+        <v>131448327</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386697</v>
+        <v>386449</v>
       </c>
       <c r="R31" t="n">
-        <v>6758686</v>
+        <v>6758648</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448329</v>
+        <v>131448386</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386494</v>
+        <v>386697</v>
       </c>
       <c r="R32" t="n">
-        <v>6758631</v>
+        <v>6758686</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3953,17 +3953,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448327</v>
+        <v>131448329</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386449</v>
+        <v>386494</v>
       </c>
       <c r="R33" t="n">
-        <v>6758648</v>
+        <v>6758631</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131448282</v>
+        <v>131440215</v>
       </c>
       <c r="B34" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,37 +4078,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386475</v>
+        <v>386402</v>
       </c>
       <c r="R34" t="n">
-        <v>6758559</v>
+        <v>6758574</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4135,19 +4135,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4162,22 +4152,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131440215</v>
+        <v>131448282</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4185,37 +4175,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386402</v>
+        <v>386475</v>
       </c>
       <c r="R35" t="n">
-        <v>6758574</v>
+        <v>6758559</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,9 +4232,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4259,12 +4259,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4274,7 +4274,7 @@
         <v>131448382</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,50 +4483,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131448321</v>
+        <v>131448347</v>
       </c>
       <c r="B38" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>386394</v>
+        <v>386553</v>
       </c>
       <c r="R38" t="n">
-        <v>6758643</v>
+        <v>6758704</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4558,7 +4553,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4568,7 +4563,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4595,10 +4590,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131448347</v>
+        <v>131448306</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4630,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>386553</v>
+        <v>386428</v>
       </c>
       <c r="R39" t="n">
-        <v>6758704</v>
+        <v>6758654</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4665,7 +4660,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4675,7 +4670,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4702,10 +4697,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131448306</v>
+        <v>131448352</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>386428</v>
+        <v>386718</v>
       </c>
       <c r="R40" t="n">
-        <v>6758654</v>
+        <v>6758619</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,7 +4767,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4782,7 +4777,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4809,10 +4804,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131448352</v>
+        <v>131448396</v>
       </c>
       <c r="B41" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4815,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386718</v>
+        <v>386635</v>
       </c>
       <c r="R41" t="n">
-        <v>6758619</v>
+        <v>6758691</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,7 +4874,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4889,7 +4884,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4909,52 +4904,57 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448396</v>
+        <v>131448321</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386635</v>
+        <v>386394</v>
       </c>
       <c r="R42" t="n">
-        <v>6758691</v>
+        <v>6758643</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5026,7 +5026,7 @@
         <v>131448339</v>
       </c>
       <c r="B43" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131440171</v>
+        <v>131448403</v>
       </c>
       <c r="B44" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5141,37 +5141,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386519</v>
+        <v>386650</v>
       </c>
       <c r="R44" t="n">
-        <v>6758682</v>
+        <v>6758630</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5198,9 +5198,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5215,22 +5225,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448346</v>
+        <v>131448289</v>
       </c>
       <c r="B45" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5238,21 +5248,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5262,10 +5272,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386558</v>
+        <v>386519</v>
       </c>
       <c r="R45" t="n">
-        <v>6758731</v>
+        <v>6758591</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5297,7 +5307,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5307,7 +5317,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5334,53 +5344,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440180</v>
+        <v>131440171</v>
       </c>
       <c r="B46" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386351</v>
+        <v>386519</v>
       </c>
       <c r="R46" t="n">
-        <v>6758581</v>
+        <v>6758682</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5439,10 +5441,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448403</v>
+        <v>131448369</v>
       </c>
       <c r="B47" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5474,10 +5476,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386650</v>
+        <v>386774</v>
       </c>
       <c r="R47" t="n">
-        <v>6758630</v>
+        <v>6758809</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5509,7 +5511,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5519,7 +5521,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5546,10 +5548,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131448289</v>
+        <v>131448346</v>
       </c>
       <c r="B48" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5557,21 +5559,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5581,10 +5583,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386519</v>
+        <v>386558</v>
       </c>
       <c r="R48" t="n">
-        <v>6758591</v>
+        <v>6758731</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,7 +5618,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5626,7 +5628,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5653,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131448369</v>
+        <v>131448322</v>
       </c>
       <c r="B49" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5688,10 +5690,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386774</v>
+        <v>386380</v>
       </c>
       <c r="R49" t="n">
-        <v>6758809</v>
+        <v>6758666</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5723,7 +5725,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5733,7 +5735,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5760,48 +5762,56 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131448322</v>
+        <v>131440180</v>
       </c>
       <c r="B50" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386380</v>
+        <v>386351</v>
       </c>
       <c r="R50" t="n">
-        <v>6758666</v>
+        <v>6758581</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5828,19 +5838,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5855,12 +5855,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5870,7 +5870,7 @@
         <v>131448328</v>
       </c>
       <c r="B51" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5974,10 +5974,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131440169</v>
+        <v>131448365</v>
       </c>
       <c r="B52" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5985,37 +5985,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386434</v>
+        <v>386808</v>
       </c>
       <c r="R52" t="n">
-        <v>6758668</v>
+        <v>6758791</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6042,9 +6042,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6059,22 +6069,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131448365</v>
+        <v>131448297</v>
       </c>
       <c r="B53" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6106,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386808</v>
+        <v>386455</v>
       </c>
       <c r="R53" t="n">
-        <v>6758791</v>
+        <v>6758589</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6141,7 +6151,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6151,7 +6161,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,10 +6188,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448297</v>
+        <v>131448330</v>
       </c>
       <c r="B54" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6213,10 +6223,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386455</v>
+        <v>386474</v>
       </c>
       <c r="R54" t="n">
-        <v>6758589</v>
+        <v>6758628</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6248,7 +6258,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6258,7 +6268,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6285,10 +6295,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131448330</v>
+        <v>131448384</v>
       </c>
       <c r="B55" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,10 +6330,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386474</v>
+        <v>386721</v>
       </c>
       <c r="R55" t="n">
-        <v>6758628</v>
+        <v>6758722</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6355,7 +6365,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6365,7 +6375,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6392,10 +6402,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131448384</v>
+        <v>131440169</v>
       </c>
       <c r="B56" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6403,37 +6413,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386721</v>
+        <v>386434</v>
       </c>
       <c r="R56" t="n">
-        <v>6758722</v>
+        <v>6758668</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6460,19 +6470,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6487,12 +6487,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
         <v>131448293</v>
       </c>
       <c r="B58" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>131448286</v>
       </c>
       <c r="B59" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>131448312</v>
       </c>
       <c r="B60" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7044,56 +7044,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131440181</v>
+        <v>131448338</v>
       </c>
       <c r="B62" t="n">
-        <v>57076</v>
+        <v>79008</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386339</v>
+        <v>386506</v>
       </c>
       <c r="R62" t="n">
-        <v>6758559</v>
+        <v>6758684</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7120,9 +7112,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7137,60 +7139,68 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131448338</v>
+        <v>131440181</v>
       </c>
       <c r="B63" t="n">
-        <v>79007</v>
+        <v>57076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>386506</v>
+        <v>386339</v>
       </c>
       <c r="R63" t="n">
-        <v>6758684</v>
+        <v>6758559</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7217,19 +7227,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7244,60 +7244,68 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131448291</v>
+        <v>131440179</v>
       </c>
       <c r="B64" t="n">
-        <v>78915</v>
+        <v>57076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>386519</v>
+        <v>386369</v>
       </c>
       <c r="R64" t="n">
-        <v>6758587</v>
+        <v>6758575</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7324,19 +7332,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7351,60 +7349,65 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131440166</v>
+        <v>131448311</v>
       </c>
       <c r="B65" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>386386</v>
+        <v>386418</v>
       </c>
       <c r="R65" t="n">
-        <v>6758567</v>
+        <v>6758590</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7431,9 +7434,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,60 +7461,68 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131448381</v>
+        <v>131440185</v>
       </c>
       <c r="B66" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386711</v>
+        <v>386353</v>
       </c>
       <c r="R66" t="n">
-        <v>6758768</v>
+        <v>6758548</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7528,19 +7549,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,60 +7566,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131440204</v>
+        <v>131448291</v>
       </c>
       <c r="B67" t="n">
-        <v>79273</v>
+        <v>78916</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386401</v>
+        <v>386519</v>
       </c>
       <c r="R67" t="n">
-        <v>6758592</v>
+        <v>6758587</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7635,9 +7646,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7652,22 +7673,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131448281</v>
+        <v>131448404</v>
       </c>
       <c r="B68" t="n">
-        <v>79006</v>
+        <v>79250</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7675,21 +7696,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7699,10 +7720,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386443</v>
+        <v>386684</v>
       </c>
       <c r="R68" t="n">
-        <v>6758546</v>
+        <v>6758614</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7734,7 +7755,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7744,7 +7765,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7764,57 +7785,52 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131448311</v>
+        <v>131448318</v>
       </c>
       <c r="B69" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>386418</v>
+        <v>386391</v>
       </c>
       <c r="R69" t="n">
-        <v>6758590</v>
+        <v>6758637</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7846,7 +7862,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7856,7 +7872,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7883,53 +7899,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131440185</v>
+        <v>131440166</v>
       </c>
       <c r="B70" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386353</v>
+        <v>386386</v>
       </c>
       <c r="R70" t="n">
-        <v>6758548</v>
+        <v>6758567</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7988,56 +7996,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131440179</v>
+        <v>131448381</v>
       </c>
       <c r="B71" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386369</v>
+        <v>386711</v>
       </c>
       <c r="R71" t="n">
-        <v>6758575</v>
+        <v>6758768</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8064,9 +8064,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8081,60 +8091,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131448404</v>
+        <v>131440204</v>
       </c>
       <c r="B72" t="n">
-        <v>79249</v>
+        <v>79274</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386684</v>
+        <v>386401</v>
       </c>
       <c r="R72" t="n">
-        <v>6758614</v>
+        <v>6758592</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8161,19 +8171,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8188,12 +8188,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8203,7 +8203,7 @@
         <v>131448323</v>
       </c>
       <c r="B73" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>131448366</v>
       </c>
       <c r="B74" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131448318</v>
+        <v>131448281</v>
       </c>
       <c r="B75" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8425,21 +8425,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386391</v>
+        <v>386443</v>
       </c>
       <c r="R75" t="n">
-        <v>6758637</v>
+        <v>6758546</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8521,10 +8521,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131448372</v>
+        <v>131440152</v>
       </c>
       <c r="B76" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8532,37 +8532,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>386764</v>
+        <v>386484</v>
       </c>
       <c r="R76" t="n">
-        <v>6758806</v>
+        <v>6758687</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8589,49 +8589,40 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131440152</v>
+        <v>131448317</v>
       </c>
       <c r="B77" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8659,17 +8650,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386484</v>
+        <v>386389</v>
       </c>
       <c r="R77" t="n">
-        <v>6758687</v>
+        <v>6758642</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8696,40 +8687,49 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131448317</v>
+        <v>131448372</v>
       </c>
       <c r="B78" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>386389</v>
+        <v>386764</v>
       </c>
       <c r="R78" t="n">
-        <v>6758642</v>
+        <v>6758806</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8836,7 +8836,7 @@
         <v>131440168</v>
       </c>
       <c r="B79" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>131448280</v>
       </c>
       <c r="B80" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>131448341</v>
       </c>
       <c r="B81" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9256,48 +9256,56 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131448343</v>
+        <v>131440190</v>
       </c>
       <c r="B83" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>386512</v>
+        <v>386402</v>
       </c>
       <c r="R83" t="n">
-        <v>6758697</v>
+        <v>6758572</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9324,19 +9332,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9351,60 +9349,68 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131448362</v>
+        <v>131440183</v>
       </c>
       <c r="B84" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>386784</v>
+        <v>386346</v>
       </c>
       <c r="R84" t="n">
-        <v>6758735</v>
+        <v>6758563</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9431,19 +9437,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9458,12 +9454,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9473,7 +9469,7 @@
         <v>131448315</v>
       </c>
       <c r="B85" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9580,7 +9576,7 @@
         <v>131448367</v>
       </c>
       <c r="B86" t="n">
-        <v>79273</v>
+        <v>79274</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9687,7 +9683,7 @@
         <v>131440172</v>
       </c>
       <c r="B87" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9781,48 +9777,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131440205</v>
+        <v>131448343</v>
       </c>
       <c r="B88" t="n">
-        <v>79273</v>
+        <v>79250</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>386413</v>
+        <v>386512</v>
       </c>
       <c r="R88" t="n">
-        <v>6758608</v>
+        <v>6758697</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9849,9 +9845,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9866,60 +9872,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131448285</v>
+        <v>131440205</v>
       </c>
       <c r="B89" t="n">
-        <v>79249</v>
+        <v>79274</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>386496</v>
+        <v>386413</v>
       </c>
       <c r="R89" t="n">
-        <v>6758565</v>
+        <v>6758608</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9946,19 +9952,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9973,22 +9969,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131448359</v>
+        <v>131448362</v>
       </c>
       <c r="B90" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9996,21 +9992,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10020,10 +10016,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>386785</v>
+        <v>386784</v>
       </c>
       <c r="R90" t="n">
-        <v>6758750</v>
+        <v>6758735</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10092,56 +10088,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131440190</v>
+        <v>131448285</v>
       </c>
       <c r="B91" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>386402</v>
+        <v>386496</v>
       </c>
       <c r="R91" t="n">
-        <v>6758572</v>
+        <v>6758565</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10168,9 +10156,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10185,68 +10183,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131440183</v>
+        <v>131448359</v>
       </c>
       <c r="B92" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>386346</v>
+        <v>386785</v>
       </c>
       <c r="R92" t="n">
-        <v>6758563</v>
+        <v>6758750</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10273,9 +10263,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10290,12 +10290,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10410,7 +10410,7 @@
         <v>131448351</v>
       </c>
       <c r="B94" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10514,10 +10514,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131448380</v>
+        <v>131440210</v>
       </c>
       <c r="B95" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10525,37 +10525,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>386713</v>
+        <v>386347</v>
       </c>
       <c r="R95" t="n">
-        <v>6758747</v>
+        <v>6758542</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10582,19 +10582,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10609,22 +10599,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131440210</v>
+        <v>131448380</v>
       </c>
       <c r="B96" t="n">
-        <v>79006</v>
+        <v>79250</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10632,37 +10622,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>386347</v>
+        <v>386713</v>
       </c>
       <c r="R96" t="n">
-        <v>6758542</v>
+        <v>6758747</v>
       </c>
       <c r="S96" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10689,9 +10679,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10706,22 +10706,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131440219</v>
+        <v>131448284</v>
       </c>
       <c r="B97" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10749,17 +10749,17 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>386495</v>
+        <v>386456</v>
       </c>
       <c r="R97" t="n">
-        <v>6758684</v>
+        <v>6758560</v>
       </c>
       <c r="S97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10786,9 +10786,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10803,22 +10813,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131448376</v>
+        <v>131440219</v>
       </c>
       <c r="B98" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10846,17 +10856,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>386715</v>
+        <v>386495</v>
       </c>
       <c r="R98" t="n">
-        <v>6758795</v>
+        <v>6758684</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10883,19 +10893,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10910,22 +10910,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131440216</v>
+        <v>131440170</v>
       </c>
       <c r="B99" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10933,21 +10933,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10957,10 +10957,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>386401</v>
+        <v>386518</v>
       </c>
       <c r="R99" t="n">
-        <v>6758591</v>
+        <v>6758680</v>
       </c>
       <c r="S99" t="n">
         <v>20</v>
@@ -11019,10 +11019,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131448345</v>
+        <v>131448376</v>
       </c>
       <c r="B100" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11054,10 +11054,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>386536</v>
+        <v>386715</v>
       </c>
       <c r="R100" t="n">
-        <v>6758715</v>
+        <v>6758795</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11126,10 +11126,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131448284</v>
+        <v>131440216</v>
       </c>
       <c r="B101" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11157,17 +11157,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>386456</v>
+        <v>386401</v>
       </c>
       <c r="R101" t="n">
-        <v>6758560</v>
+        <v>6758591</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11194,19 +11194,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11221,22 +11211,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131440170</v>
+        <v>131448345</v>
       </c>
       <c r="B102" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11244,37 +11234,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>386518</v>
+        <v>386536</v>
       </c>
       <c r="R102" t="n">
-        <v>6758680</v>
+        <v>6758715</v>
       </c>
       <c r="S102" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11301,9 +11291,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11318,12 +11318,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131448399</v>
+        <v>131440225</v>
       </c>
       <c r="B104" t="n">
-        <v>79249</v>
+        <v>78916</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11446,37 +11446,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>386647</v>
+        <v>386426</v>
       </c>
       <c r="R104" t="n">
-        <v>6758685</v>
+        <v>6758644</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11503,19 +11503,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11530,22 +11520,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131448304</v>
+        <v>131448399</v>
       </c>
       <c r="B105" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11577,10 +11567,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>386423</v>
+        <v>386647</v>
       </c>
       <c r="R105" t="n">
-        <v>6758618</v>
+        <v>6758685</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11612,7 +11602,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11622,7 +11612,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11642,17 +11632,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131448337</v>
+        <v>131448304</v>
       </c>
       <c r="B106" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11684,10 +11674,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>386503</v>
+        <v>386423</v>
       </c>
       <c r="R106" t="n">
-        <v>6758670</v>
+        <v>6758618</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11719,7 +11709,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11729,7 +11719,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11756,10 +11746,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131440217</v>
+        <v>131448337</v>
       </c>
       <c r="B107" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11787,17 +11777,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>386476</v>
+        <v>386503</v>
       </c>
       <c r="R107" t="n">
-        <v>6758669</v>
+        <v>6758670</v>
       </c>
       <c r="S107" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11824,9 +11814,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11841,22 +11841,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131440225</v>
+        <v>131440217</v>
       </c>
       <c r="B108" t="n">
-        <v>78915</v>
+        <v>79250</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11864,21 +11864,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11888,10 +11888,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>386426</v>
+        <v>386476</v>
       </c>
       <c r="R108" t="n">
-        <v>6758644</v>
+        <v>6758669</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -11950,7 +11950,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131448303</v>
+        <v>131440182</v>
       </c>
       <c r="B109" t="n">
         <v>57076</v>
@@ -11979,24 +11979,27 @@
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>386417</v>
+        <v>386348</v>
       </c>
       <c r="R109" t="n">
-        <v>6758612</v>
+        <v>6758562</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12023,19 +12026,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12050,57 +12043,62 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131448401</v>
+        <v>131448303</v>
       </c>
       <c r="B110" t="n">
-        <v>79249</v>
+        <v>57076</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>386677</v>
+        <v>386417</v>
       </c>
       <c r="R110" t="n">
-        <v>6758630</v>
+        <v>6758612</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12132,7 +12130,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12142,7 +12140,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12169,48 +12167,48 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131440206</v>
+        <v>131448401</v>
       </c>
       <c r="B111" t="n">
-        <v>79273</v>
+        <v>79250</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>386478</v>
+        <v>386677</v>
       </c>
       <c r="R111" t="n">
-        <v>6758669</v>
+        <v>6758630</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12237,9 +12235,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12254,22 +12262,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131440182</v>
+        <v>131440206</v>
       </c>
       <c r="B112" t="n">
-        <v>57076</v>
+        <v>79274</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12277,42 +12285,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>386348</v>
+        <v>386478</v>
       </c>
       <c r="R112" t="n">
-        <v>6758562</v>
+        <v>6758669</v>
       </c>
       <c r="S112" t="n">
         <v>20</v>
@@ -12371,10 +12371,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131440224</v>
+        <v>131448308</v>
       </c>
       <c r="B113" t="n">
-        <v>78915</v>
+        <v>79869</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12382,37 +12382,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>386364</v>
+        <v>386413</v>
       </c>
       <c r="R113" t="n">
-        <v>6758576</v>
+        <v>6758591</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12439,9 +12439,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12456,12 +12466,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12471,7 +12481,7 @@
         <v>131448335</v>
       </c>
       <c r="B114" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12575,45 +12585,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131448308</v>
+        <v>131448287</v>
       </c>
       <c r="B115" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>386413</v>
+        <v>386516</v>
       </c>
       <c r="R115" t="n">
-        <v>6758591</v>
+        <v>6758592</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12645,7 +12660,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12655,7 +12670,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12682,53 +12697,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131448287</v>
+        <v>131440224</v>
       </c>
       <c r="B116" t="n">
-        <v>57076</v>
+        <v>78916</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>386516</v>
+        <v>386364</v>
       </c>
       <c r="R116" t="n">
-        <v>6758592</v>
+        <v>6758576</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12755,19 +12765,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12782,12 +12782,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12797,7 +12797,7 @@
         <v>131448374</v>
       </c>
       <c r="B117" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12901,53 +12901,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131448268</v>
+        <v>131440167</v>
       </c>
       <c r="B118" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>386348</v>
+        <v>386367</v>
       </c>
       <c r="R118" t="n">
-        <v>6758527</v>
+        <v>6758574</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12974,19 +12969,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13001,62 +12986,57 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131448320</v>
+        <v>131448301</v>
       </c>
       <c r="B119" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>386392</v>
+        <v>386445</v>
       </c>
       <c r="R119" t="n">
-        <v>6758650</v>
+        <v>6758588</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13088,7 +13068,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13098,7 +13078,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13125,32 +13105,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131448301</v>
+        <v>131448383</v>
       </c>
       <c r="B120" t="n">
-        <v>79249</v>
+        <v>79274</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13160,10 +13140,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>386445</v>
+        <v>386711</v>
       </c>
       <c r="R120" t="n">
-        <v>6758588</v>
+        <v>6758695</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13195,7 +13175,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13205,7 +13185,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13232,48 +13212,53 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131440167</v>
+        <v>131448268</v>
       </c>
       <c r="B121" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>386367</v>
+        <v>386348</v>
       </c>
       <c r="R121" t="n">
-        <v>6758574</v>
+        <v>6758527</v>
       </c>
       <c r="S121" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13300,9 +13285,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13317,22 +13312,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131448383</v>
+        <v>131448320</v>
       </c>
       <c r="B122" t="n">
-        <v>79273</v>
+        <v>57076</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13340,34 +13335,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>386711</v>
+        <v>386392</v>
       </c>
       <c r="R122" t="n">
-        <v>6758695</v>
+        <v>6758650</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13439,7 +13439,7 @@
         <v>131448325</v>
       </c>
       <c r="B123" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>131448405</v>
       </c>
       <c r="B124" t="n">
-        <v>78915</v>
+        <v>78916</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13643,17 +13643,17 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131448342</v>
+        <v>131448397</v>
       </c>
       <c r="B125" t="n">
-        <v>79868</v>
+        <v>79250</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13661,21 +13661,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13685,10 +13685,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>386512</v>
+        <v>386638</v>
       </c>
       <c r="R125" t="n">
-        <v>6758697</v>
+        <v>6758692</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13750,17 +13750,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131448397</v>
+        <v>131448342</v>
       </c>
       <c r="B126" t="n">
-        <v>79249</v>
+        <v>79869</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13768,21 +13768,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13792,10 +13792,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>386638</v>
+        <v>386512</v>
       </c>
       <c r="R126" t="n">
-        <v>6758692</v>
+        <v>6758697</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -675,48 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131448402</v>
+        <v>131440184</v>
       </c>
       <c r="B2" t="n">
-        <v>78916</v>
+        <v>57076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386676</v>
+        <v>386349</v>
       </c>
       <c r="R2" t="n">
-        <v>6758633</v>
+        <v>6758545</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +751,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,68 +768,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131440184</v>
+        <v>131448402</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>78916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386349</v>
+        <v>386676</v>
       </c>
       <c r="R3" t="n">
-        <v>6758545</v>
+        <v>6758633</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,9 +848,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448370</v>
+        <v>131448259</v>
       </c>
       <c r="B17" t="n">
-        <v>79840</v>
+        <v>78916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386751</v>
+        <v>386484</v>
       </c>
       <c r="R17" t="n">
-        <v>6758793</v>
+        <v>6758522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131448259</v>
+        <v>131448344</v>
       </c>
       <c r="B18" t="n">
         <v>78916</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386484</v>
+        <v>386506</v>
       </c>
       <c r="R18" t="n">
-        <v>6758522</v>
+        <v>6758691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448344</v>
+        <v>131448363</v>
       </c>
       <c r="B19" t="n">
         <v>78916</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386506</v>
+        <v>386784</v>
       </c>
       <c r="R19" t="n">
-        <v>6758691</v>
+        <v>6758735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448363</v>
+        <v>131448379</v>
       </c>
       <c r="B20" t="n">
         <v>78916</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386784</v>
+        <v>386696</v>
       </c>
       <c r="R20" t="n">
-        <v>6758735</v>
+        <v>6758781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448379</v>
+        <v>131448299</v>
       </c>
       <c r="B21" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386696</v>
+        <v>386440</v>
       </c>
       <c r="R21" t="n">
-        <v>6758781</v>
+        <v>6758599</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131440220</v>
+        <v>131448295</v>
       </c>
       <c r="B22" t="n">
         <v>79250</v>
@@ -2826,17 +2826,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386519</v>
+        <v>386474</v>
       </c>
       <c r="R22" t="n">
-        <v>6758698</v>
+        <v>6758587</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2863,9 +2863,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2880,19 +2890,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131448299</v>
+        <v>131448375</v>
       </c>
       <c r="B23" t="n">
         <v>79250</v>
@@ -2927,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386440</v>
+        <v>386743</v>
       </c>
       <c r="R23" t="n">
-        <v>6758599</v>
+        <v>6758789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,7 +2972,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2972,7 +2982,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448295</v>
+        <v>131440220</v>
       </c>
       <c r="B24" t="n">
         <v>79250</v>
@@ -3030,17 +3040,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386474</v>
+        <v>386519</v>
       </c>
       <c r="R24" t="n">
-        <v>6758587</v>
+        <v>6758698</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3067,19 +3077,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3094,60 +3094,68 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448375</v>
+        <v>131440191</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386743</v>
+        <v>386397</v>
       </c>
       <c r="R25" t="n">
-        <v>6758789</v>
+        <v>6758574</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3174,19 +3182,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3201,68 +3199,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131440191</v>
+        <v>131448350</v>
       </c>
       <c r="B26" t="n">
-        <v>57076</v>
+        <v>79008</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386397</v>
+        <v>386644</v>
       </c>
       <c r="R26" t="n">
-        <v>6758574</v>
+        <v>6758591</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3289,9 +3279,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3306,22 +3306,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131448350</v>
+        <v>131448370</v>
       </c>
       <c r="B27" t="n">
-        <v>79008</v>
+        <v>79840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386644</v>
+        <v>386751</v>
       </c>
       <c r="R27" t="n">
-        <v>6758591</v>
+        <v>6758793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448292</v>
+        <v>131448409</v>
       </c>
       <c r="B28" t="n">
         <v>79250</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386495</v>
+        <v>386711</v>
       </c>
       <c r="R28" t="n">
-        <v>6758597</v>
+        <v>6758601</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448368</v>
+        <v>131448327</v>
       </c>
       <c r="B29" t="n">
         <v>79250</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386787</v>
+        <v>386449</v>
       </c>
       <c r="R29" t="n">
-        <v>6758812</v>
+        <v>6758648</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448409</v>
+        <v>131448292</v>
       </c>
       <c r="B30" t="n">
         <v>79250</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386711</v>
+        <v>386495</v>
       </c>
       <c r="R30" t="n">
-        <v>6758601</v>
+        <v>6758597</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3739,14 +3739,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448327</v>
+        <v>131448368</v>
       </c>
       <c r="B31" t="n">
         <v>79250</v>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386449</v>
+        <v>386787</v>
       </c>
       <c r="R31" t="n">
-        <v>6758648</v>
+        <v>6758812</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131440215</v>
+        <v>131448282</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,37 +4078,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386402</v>
+        <v>386475</v>
       </c>
       <c r="R34" t="n">
-        <v>6758574</v>
+        <v>6758559</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4135,9 +4135,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,22 +4162,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448282</v>
+        <v>131448382</v>
       </c>
       <c r="B35" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,21 +4185,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4199,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386475</v>
+        <v>386718</v>
       </c>
       <c r="R35" t="n">
-        <v>6758559</v>
+        <v>6758734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4234,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4244,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4271,48 +4281,56 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131448382</v>
+        <v>131440192</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386718</v>
+        <v>386414</v>
       </c>
       <c r="R36" t="n">
-        <v>6758734</v>
+        <v>6758608</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4339,19 +4357,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,65 +4374,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131440192</v>
+        <v>131440215</v>
       </c>
       <c r="B37" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386414</v>
+        <v>386402</v>
       </c>
       <c r="R37" t="n">
-        <v>6758608</v>
+        <v>6758574</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131448339</v>
+        <v>131448403</v>
       </c>
       <c r="B43" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386506</v>
+        <v>386650</v>
       </c>
       <c r="R43" t="n">
-        <v>6758684</v>
+        <v>6758630</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5130,7 +5130,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448403</v>
+        <v>131448289</v>
       </c>
       <c r="B44" t="n">
         <v>79250</v>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386650</v>
+        <v>386519</v>
       </c>
       <c r="R44" t="n">
-        <v>6758630</v>
+        <v>6758591</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448289</v>
+        <v>131440171</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5248,37 +5248,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
         <v>386519</v>
       </c>
       <c r="R45" t="n">
-        <v>6758591</v>
+        <v>6758682</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5305,19 +5305,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5332,22 +5322,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440171</v>
+        <v>131448369</v>
       </c>
       <c r="B46" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5355,37 +5345,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386519</v>
+        <v>386774</v>
       </c>
       <c r="R46" t="n">
-        <v>6758682</v>
+        <v>6758809</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5412,9 +5402,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5429,22 +5429,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448369</v>
+        <v>131448346</v>
       </c>
       <c r="B47" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386774</v>
+        <v>386558</v>
       </c>
       <c r="R47" t="n">
-        <v>6758809</v>
+        <v>6758731</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5548,10 +5548,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131448346</v>
+        <v>131448322</v>
       </c>
       <c r="B48" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5559,21 +5559,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5583,10 +5583,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386558</v>
+        <v>386380</v>
       </c>
       <c r="R48" t="n">
-        <v>6758731</v>
+        <v>6758666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131448322</v>
+        <v>131448339</v>
       </c>
       <c r="B49" t="n">
-        <v>79250</v>
+        <v>78916</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5666,21 +5666,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386380</v>
+        <v>386506</v>
       </c>
       <c r="R49" t="n">
-        <v>6758666</v>
+        <v>6758684</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6611,45 +6611,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131448293</v>
+        <v>131448283</v>
       </c>
       <c r="B58" t="n">
-        <v>78916</v>
+        <v>57076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386508</v>
+        <v>386456</v>
       </c>
       <c r="R58" t="n">
-        <v>6758593</v>
+        <v>6758560</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6681,7 +6686,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6691,7 +6696,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6718,48 +6723,56 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131448286</v>
+        <v>131440181</v>
       </c>
       <c r="B59" t="n">
-        <v>78916</v>
+        <v>57076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386475</v>
+        <v>386339</v>
       </c>
       <c r="R59" t="n">
         <v>6758559</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6786,19 +6799,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6813,22 +6816,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131448312</v>
+        <v>131448293</v>
       </c>
       <c r="B60" t="n">
-        <v>79869</v>
+        <v>78916</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6836,21 +6839,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6860,10 +6863,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>386410</v>
+        <v>386508</v>
       </c>
       <c r="R60" t="n">
-        <v>6758596</v>
+        <v>6758593</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6895,7 +6898,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6905,7 +6908,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6932,50 +6935,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131448283</v>
+        <v>131448286</v>
       </c>
       <c r="B61" t="n">
-        <v>57076</v>
+        <v>78916</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>386456</v>
+        <v>386475</v>
       </c>
       <c r="R61" t="n">
-        <v>6758560</v>
+        <v>6758559</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7007,7 +7005,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7017,7 +7015,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7044,10 +7042,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131448338</v>
+        <v>131448312</v>
       </c>
       <c r="B62" t="n">
-        <v>79008</v>
+        <v>79869</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7055,21 +7053,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7079,10 +7077,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386506</v>
+        <v>386410</v>
       </c>
       <c r="R62" t="n">
-        <v>6758684</v>
+        <v>6758596</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7114,7 +7112,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7124,7 +7122,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7151,56 +7149,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131440181</v>
+        <v>131448338</v>
       </c>
       <c r="B63" t="n">
-        <v>57076</v>
+        <v>79008</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>386339</v>
+        <v>386506</v>
       </c>
       <c r="R63" t="n">
-        <v>6758559</v>
+        <v>6758684</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7227,9 +7217,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7244,68 +7244,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131440179</v>
+        <v>131448291</v>
       </c>
       <c r="B64" t="n">
-        <v>57076</v>
+        <v>78916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>386369</v>
+        <v>386519</v>
       </c>
       <c r="R64" t="n">
-        <v>6758575</v>
+        <v>6758587</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7332,9 +7324,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7349,62 +7351,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131448311</v>
+        <v>131448404</v>
       </c>
       <c r="B65" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>386418</v>
+        <v>386684</v>
       </c>
       <c r="R65" t="n">
-        <v>6758590</v>
+        <v>6758614</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7436,7 +7433,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7446,7 +7443,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7473,56 +7470,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131440185</v>
+        <v>131448318</v>
       </c>
       <c r="B66" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386353</v>
+        <v>386391</v>
       </c>
       <c r="R66" t="n">
-        <v>6758548</v>
+        <v>6758637</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7549,9 +7538,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7566,22 +7565,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131448291</v>
+        <v>131440166</v>
       </c>
       <c r="B67" t="n">
-        <v>78916</v>
+        <v>79869</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7589,37 +7588,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386519</v>
+        <v>386386</v>
       </c>
       <c r="R67" t="n">
-        <v>6758587</v>
+        <v>6758567</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7646,19 +7645,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7673,19 +7662,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131448404</v>
+        <v>131448381</v>
       </c>
       <c r="B68" t="n">
         <v>79250</v>
@@ -7720,10 +7709,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386684</v>
+        <v>386711</v>
       </c>
       <c r="R68" t="n">
-        <v>6758614</v>
+        <v>6758768</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7755,7 +7744,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7765,7 +7754,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7785,55 +7774,55 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131448318</v>
+        <v>131440204</v>
       </c>
       <c r="B69" t="n">
-        <v>79250</v>
+        <v>79274</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>386391</v>
+        <v>386401</v>
       </c>
       <c r="R69" t="n">
-        <v>6758637</v>
+        <v>6758592</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7860,19 +7849,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7887,22 +7866,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131440166</v>
+        <v>131448323</v>
       </c>
       <c r="B70" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7910,37 +7889,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386386</v>
+        <v>386418</v>
       </c>
       <c r="R70" t="n">
-        <v>6758567</v>
+        <v>6758667</v>
       </c>
       <c r="S70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7967,9 +7946,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7984,19 +7973,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131448381</v>
+        <v>131448366</v>
       </c>
       <c r="B71" t="n">
         <v>79250</v>
@@ -8031,10 +8020,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386711</v>
+        <v>386800</v>
       </c>
       <c r="R71" t="n">
-        <v>6758768</v>
+        <v>6758785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8066,7 +8055,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8076,7 +8065,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8103,48 +8092,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131440204</v>
+        <v>131448281</v>
       </c>
       <c r="B72" t="n">
-        <v>79274</v>
+        <v>79007</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386401</v>
+        <v>386443</v>
       </c>
       <c r="R72" t="n">
-        <v>6758592</v>
+        <v>6758546</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8171,9 +8160,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8188,47 +8187,52 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131448323</v>
+        <v>131448311</v>
       </c>
       <c r="B73" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
@@ -8238,7 +8242,7 @@
         <v>386418</v>
       </c>
       <c r="R73" t="n">
-        <v>6758667</v>
+        <v>6758590</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8270,7 +8274,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8280,7 +8284,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8307,48 +8311,56 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131448366</v>
+        <v>131440185</v>
       </c>
       <c r="B74" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386800</v>
+        <v>386353</v>
       </c>
       <c r="R74" t="n">
-        <v>6758785</v>
+        <v>6758548</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8375,19 +8387,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8402,60 +8404,68 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131448281</v>
+        <v>131440179</v>
       </c>
       <c r="B75" t="n">
-        <v>79007</v>
+        <v>57076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386443</v>
+        <v>386369</v>
       </c>
       <c r="R75" t="n">
-        <v>6758546</v>
+        <v>6758575</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8482,19 +8492,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8509,12 +8509,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9256,56 +9256,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131440190</v>
+        <v>131448315</v>
       </c>
       <c r="B83" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
         <v>386402</v>
       </c>
       <c r="R83" t="n">
-        <v>6758572</v>
+        <v>6758596</v>
       </c>
       <c r="S83" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9332,9 +9324,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9349,22 +9351,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131440183</v>
+        <v>131448367</v>
       </c>
       <c r="B84" t="n">
-        <v>57076</v>
+        <v>79274</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9372,45 +9374,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>386346</v>
+        <v>386774</v>
       </c>
       <c r="R84" t="n">
-        <v>6758563</v>
+        <v>6758809</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9437,9 +9431,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9454,22 +9458,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131448315</v>
+        <v>131440172</v>
       </c>
       <c r="B85" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9477,37 +9481,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>386402</v>
+        <v>386524</v>
       </c>
       <c r="R85" t="n">
-        <v>6758596</v>
+        <v>6758661</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9534,19 +9538,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9561,44 +9555,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131448367</v>
+        <v>131448343</v>
       </c>
       <c r="B86" t="n">
-        <v>79274</v>
+        <v>79250</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9608,10 +9602,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>386774</v>
+        <v>386512</v>
       </c>
       <c r="R86" t="n">
-        <v>6758809</v>
+        <v>6758697</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9643,7 +9637,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9653,7 +9647,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9680,32 +9674,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131440172</v>
+        <v>131440205</v>
       </c>
       <c r="B87" t="n">
-        <v>79869</v>
+        <v>79274</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9715,10 +9709,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>386524</v>
+        <v>386413</v>
       </c>
       <c r="R87" t="n">
-        <v>6758661</v>
+        <v>6758608</v>
       </c>
       <c r="S87" t="n">
         <v>20</v>
@@ -9777,7 +9771,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131448343</v>
+        <v>131448362</v>
       </c>
       <c r="B88" t="n">
         <v>79250</v>
@@ -9812,10 +9806,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>386512</v>
+        <v>386784</v>
       </c>
       <c r="R88" t="n">
-        <v>6758697</v>
+        <v>6758735</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9847,7 +9841,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9857,7 +9851,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9884,48 +9878,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131440205</v>
+        <v>131448285</v>
       </c>
       <c r="B89" t="n">
-        <v>79274</v>
+        <v>79250</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>386413</v>
+        <v>386496</v>
       </c>
       <c r="R89" t="n">
-        <v>6758608</v>
+        <v>6758565</v>
       </c>
       <c r="S89" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9952,9 +9946,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9969,22 +9973,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131448362</v>
+        <v>131448359</v>
       </c>
       <c r="B90" t="n">
-        <v>79250</v>
+        <v>79869</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9992,21 +9996,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10016,10 +10020,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>386784</v>
+        <v>386785</v>
       </c>
       <c r="R90" t="n">
-        <v>6758735</v>
+        <v>6758750</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10088,48 +10092,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131448285</v>
+        <v>131440190</v>
       </c>
       <c r="B91" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>386496</v>
+        <v>386402</v>
       </c>
       <c r="R91" t="n">
-        <v>6758565</v>
+        <v>6758572</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10156,19 +10168,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10183,60 +10185,68 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131448359</v>
+        <v>131440183</v>
       </c>
       <c r="B92" t="n">
-        <v>79869</v>
+        <v>57076</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>386785</v>
+        <v>386346</v>
       </c>
       <c r="R92" t="n">
-        <v>6758750</v>
+        <v>6758563</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10263,19 +10273,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10290,68 +10290,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131440189</v>
+        <v>131448351</v>
       </c>
       <c r="B93" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>386396</v>
+        <v>386637</v>
       </c>
       <c r="R93" t="n">
-        <v>6758549</v>
+        <v>6758584</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10378,9 +10370,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10395,22 +10397,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131448351</v>
+        <v>131440210</v>
       </c>
       <c r="B94" t="n">
-        <v>79250</v>
+        <v>79007</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10418,37 +10420,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>386637</v>
+        <v>386347</v>
       </c>
       <c r="R94" t="n">
-        <v>6758584</v>
+        <v>6758542</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10475,19 +10477,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10502,22 +10494,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131440210</v>
+        <v>131448380</v>
       </c>
       <c r="B95" t="n">
-        <v>79007</v>
+        <v>79250</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10525,37 +10517,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>386347</v>
+        <v>386713</v>
       </c>
       <c r="R95" t="n">
-        <v>6758542</v>
+        <v>6758747</v>
       </c>
       <c r="S95" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10582,9 +10574,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10599,60 +10601,68 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131448380</v>
+        <v>131440189</v>
       </c>
       <c r="B96" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>386713</v>
+        <v>386396</v>
       </c>
       <c r="R96" t="n">
-        <v>6758747</v>
+        <v>6758549</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10679,19 +10689,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10706,12 +10706,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12371,10 +12371,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131448308</v>
+        <v>131440224</v>
       </c>
       <c r="B113" t="n">
-        <v>79869</v>
+        <v>78916</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12382,37 +12382,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>386413</v>
+        <v>386364</v>
       </c>
       <c r="R113" t="n">
-        <v>6758591</v>
+        <v>6758576</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12439,19 +12439,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,57 +12456,62 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131448335</v>
+        <v>131448287</v>
       </c>
       <c r="B114" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>386526</v>
+        <v>386516</v>
       </c>
       <c r="R114" t="n">
-        <v>6758655</v>
+        <v>6758592</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12548,7 +12543,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12558,7 +12553,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12585,50 +12580,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131448287</v>
+        <v>131448308</v>
       </c>
       <c r="B115" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>386516</v>
+        <v>386413</v>
       </c>
       <c r="R115" t="n">
-        <v>6758592</v>
+        <v>6758591</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12660,7 +12650,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12670,7 +12660,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12697,10 +12687,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131440224</v>
+        <v>131448335</v>
       </c>
       <c r="B116" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12708,37 +12698,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>386364</v>
+        <v>386526</v>
       </c>
       <c r="R116" t="n">
-        <v>6758576</v>
+        <v>6758655</v>
       </c>
       <c r="S116" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12765,9 +12755,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12782,12 +12782,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131448387</v>
+        <v>131448324</v>
       </c>
       <c r="B8" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386707</v>
+        <v>386405</v>
       </c>
       <c r="R8" t="n">
-        <v>6758689</v>
+        <v>6758668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131440187</v>
+        <v>131440197</v>
       </c>
       <c r="B9" t="n">
-        <v>57076</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,42 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386361</v>
+        <v>386393</v>
       </c>
       <c r="R9" t="n">
-        <v>6758535</v>
+        <v>6758564</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1509,6 +1501,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131440186</v>
+        <v>131448356</v>
       </c>
       <c r="B10" t="n">
-        <v>57076</v>
+        <v>79274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,45 +1531,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386354</v>
+        <v>386780</v>
       </c>
       <c r="R10" t="n">
-        <v>6758536</v>
+        <v>6758712</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,9 +1588,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1620,65 +1615,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131448319</v>
+        <v>131440221</v>
       </c>
       <c r="B11" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386383</v>
+        <v>386525</v>
       </c>
       <c r="R11" t="n">
-        <v>6758654</v>
+        <v>6758695</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1705,19 +1695,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,22 +1712,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131448324</v>
+        <v>131448387</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>78916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,21 +1735,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386405</v>
+        <v>386707</v>
       </c>
       <c r="R12" t="n">
-        <v>6758668</v>
+        <v>6758689</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,7 +1794,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1824,7 +1804,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,48 +1831,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131440197</v>
+        <v>131448406</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>79869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386393</v>
+        <v>386719</v>
       </c>
       <c r="R13" t="n">
-        <v>6758564</v>
+        <v>6758587</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1919,78 +1899,95 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131448406</v>
+        <v>131440187</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>57076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386719</v>
+        <v>386361</v>
       </c>
       <c r="R14" t="n">
-        <v>6758587</v>
+        <v>6758535</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,19 +2014,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2044,22 +2031,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131448356</v>
+        <v>131440186</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>57076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,37 +2054,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386780</v>
+        <v>386354</v>
       </c>
       <c r="R15" t="n">
-        <v>6758712</v>
+        <v>6758536</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,19 +2119,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,60 +2136,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131440221</v>
+        <v>131448319</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386525</v>
+        <v>386383</v>
       </c>
       <c r="R16" t="n">
-        <v>6758695</v>
+        <v>6758654</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2221,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,22 +2248,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448259</v>
+        <v>131448299</v>
       </c>
       <c r="B17" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386484</v>
+        <v>386440</v>
       </c>
       <c r="R17" t="n">
-        <v>6758522</v>
+        <v>6758599</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131448344</v>
+        <v>131448295</v>
       </c>
       <c r="B18" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386506</v>
+        <v>386474</v>
       </c>
       <c r="R18" t="n">
-        <v>6758691</v>
+        <v>6758587</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448363</v>
+        <v>131448375</v>
       </c>
       <c r="B19" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386784</v>
+        <v>386743</v>
       </c>
       <c r="R19" t="n">
-        <v>6758735</v>
+        <v>6758789</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448379</v>
+        <v>131448350</v>
       </c>
       <c r="B20" t="n">
-        <v>78916</v>
+        <v>79008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386696</v>
+        <v>386644</v>
       </c>
       <c r="R20" t="n">
-        <v>6758781</v>
+        <v>6758591</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448299</v>
+        <v>131448370</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386440</v>
+        <v>386751</v>
       </c>
       <c r="R21" t="n">
-        <v>6758599</v>
+        <v>6758793</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131448295</v>
+        <v>131440220</v>
       </c>
       <c r="B22" t="n">
         <v>79250</v>
@@ -2826,17 +2826,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386474</v>
+        <v>386519</v>
       </c>
       <c r="R22" t="n">
-        <v>6758587</v>
+        <v>6758698</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2863,19 +2863,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,60 +2880,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131448375</v>
+        <v>131440191</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386743</v>
+        <v>386397</v>
       </c>
       <c r="R23" t="n">
-        <v>6758789</v>
+        <v>6758574</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2970,19 +2968,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,22 +2985,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131440220</v>
+        <v>131448259</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>78916</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3020,37 +3008,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386519</v>
+        <v>386484</v>
       </c>
       <c r="R24" t="n">
-        <v>6758698</v>
+        <v>6758522</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3077,9 +3065,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3094,68 +3092,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131440191</v>
+        <v>131448344</v>
       </c>
       <c r="B25" t="n">
-        <v>57076</v>
+        <v>78916</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386397</v>
+        <v>386506</v>
       </c>
       <c r="R25" t="n">
-        <v>6758574</v>
+        <v>6758691</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3182,9 +3172,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3199,22 +3199,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448350</v>
+        <v>131448363</v>
       </c>
       <c r="B26" t="n">
-        <v>79008</v>
+        <v>78916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386644</v>
+        <v>386784</v>
       </c>
       <c r="R26" t="n">
-        <v>6758591</v>
+        <v>6758735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131448370</v>
+        <v>131448379</v>
       </c>
       <c r="B27" t="n">
-        <v>79840</v>
+        <v>78916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386751</v>
+        <v>386696</v>
       </c>
       <c r="R27" t="n">
-        <v>6758793</v>
+        <v>6758781</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,7 +3425,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448409</v>
+        <v>131448292</v>
       </c>
       <c r="B28" t="n">
         <v>79250</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386711</v>
+        <v>386495</v>
       </c>
       <c r="R28" t="n">
-        <v>6758601</v>
+        <v>6758597</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,7 +3532,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448327</v>
+        <v>131448368</v>
       </c>
       <c r="B29" t="n">
         <v>79250</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386449</v>
+        <v>386787</v>
       </c>
       <c r="R29" t="n">
-        <v>6758648</v>
+        <v>6758812</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,7 +3639,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131448292</v>
+        <v>131448409</v>
       </c>
       <c r="B30" t="n">
         <v>79250</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>386495</v>
+        <v>386711</v>
       </c>
       <c r="R30" t="n">
-        <v>6758597</v>
+        <v>6758601</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,7 +3746,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448368</v>
+        <v>131448327</v>
       </c>
       <c r="B31" t="n">
         <v>79250</v>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386787</v>
+        <v>386449</v>
       </c>
       <c r="R31" t="n">
-        <v>6758812</v>
+        <v>6758648</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4281,53 +4281,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131440192</v>
+        <v>131440215</v>
       </c>
       <c r="B36" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386414</v>
+        <v>386402</v>
       </c>
       <c r="R36" t="n">
-        <v>6758608</v>
+        <v>6758574</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4386,45 +4378,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131440215</v>
+        <v>131440192</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386402</v>
+        <v>386414</v>
       </c>
       <c r="R37" t="n">
-        <v>6758574</v>
+        <v>6758608</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131448403</v>
+        <v>131448339</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>78916</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386650</v>
+        <v>386506</v>
       </c>
       <c r="R43" t="n">
-        <v>6758630</v>
+        <v>6758684</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5130,48 +5130,56 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448289</v>
+        <v>131440180</v>
       </c>
       <c r="B44" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386519</v>
+        <v>386351</v>
       </c>
       <c r="R44" t="n">
-        <v>6758591</v>
+        <v>6758581</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5198,19 +5206,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5225,22 +5223,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131440171</v>
+        <v>131448403</v>
       </c>
       <c r="B45" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5248,37 +5246,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386519</v>
+        <v>386650</v>
       </c>
       <c r="R45" t="n">
-        <v>6758682</v>
+        <v>6758630</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5305,9 +5303,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5322,19 +5330,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131448369</v>
+        <v>131448289</v>
       </c>
       <c r="B46" t="n">
         <v>79250</v>
@@ -5369,10 +5377,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386774</v>
+        <v>386519</v>
       </c>
       <c r="R46" t="n">
-        <v>6758809</v>
+        <v>6758591</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5404,7 +5412,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5414,7 +5422,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5441,7 +5449,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448346</v>
+        <v>131440171</v>
       </c>
       <c r="B47" t="n">
         <v>79869</v>
@@ -5472,17 +5480,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386558</v>
+        <v>386519</v>
       </c>
       <c r="R47" t="n">
-        <v>6758731</v>
+        <v>6758682</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5509,19 +5517,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5536,19 +5534,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131448322</v>
+        <v>131448369</v>
       </c>
       <c r="B48" t="n">
         <v>79250</v>
@@ -5583,10 +5581,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386380</v>
+        <v>386774</v>
       </c>
       <c r="R48" t="n">
-        <v>6758666</v>
+        <v>6758809</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5618,7 +5616,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5628,7 +5626,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,10 +5653,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131448339</v>
+        <v>131448346</v>
       </c>
       <c r="B49" t="n">
-        <v>78916</v>
+        <v>79869</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5666,21 +5664,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5690,10 +5688,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386506</v>
+        <v>386558</v>
       </c>
       <c r="R49" t="n">
-        <v>6758684</v>
+        <v>6758731</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5725,7 +5723,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5735,7 +5733,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5762,56 +5760,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131440180</v>
+        <v>131448322</v>
       </c>
       <c r="B50" t="n">
-        <v>57076</v>
+        <v>79250</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386351</v>
+        <v>386380</v>
       </c>
       <c r="R50" t="n">
-        <v>6758581</v>
+        <v>6758666</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5838,9 +5828,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5855,57 +5855,62 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131448328</v>
+        <v>131448364</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>57076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386450</v>
+        <v>386784</v>
       </c>
       <c r="R51" t="n">
-        <v>6758649</v>
+        <v>6758773</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,7 +5942,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5947,7 +5952,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5974,7 +5979,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131448365</v>
+        <v>131448328</v>
       </c>
       <c r="B52" t="n">
         <v>79250</v>
@@ -6009,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386808</v>
+        <v>386450</v>
       </c>
       <c r="R52" t="n">
-        <v>6758791</v>
+        <v>6758649</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6044,7 +6049,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6054,7 +6059,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6081,7 +6086,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131448297</v>
+        <v>131448365</v>
       </c>
       <c r="B53" t="n">
         <v>79250</v>
@@ -6116,10 +6121,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386455</v>
+        <v>386808</v>
       </c>
       <c r="R53" t="n">
-        <v>6758589</v>
+        <v>6758791</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6151,7 +6156,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6161,7 +6166,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6188,7 +6193,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448330</v>
+        <v>131448297</v>
       </c>
       <c r="B54" t="n">
         <v>79250</v>
@@ -6223,10 +6228,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386474</v>
+        <v>386455</v>
       </c>
       <c r="R54" t="n">
-        <v>6758628</v>
+        <v>6758589</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6258,7 +6263,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6268,7 +6273,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6295,7 +6300,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131448384</v>
+        <v>131448330</v>
       </c>
       <c r="B55" t="n">
         <v>79250</v>
@@ -6330,10 +6335,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386721</v>
+        <v>386474</v>
       </c>
       <c r="R55" t="n">
-        <v>6758722</v>
+        <v>6758628</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6365,7 +6370,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6375,7 +6380,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6402,10 +6407,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131440169</v>
+        <v>131448384</v>
       </c>
       <c r="B56" t="n">
-        <v>79869</v>
+        <v>79250</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6413,37 +6418,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386434</v>
+        <v>386721</v>
       </c>
       <c r="R56" t="n">
-        <v>6758668</v>
+        <v>6758722</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6470,9 +6475,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6487,65 +6502,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131448364</v>
+        <v>131440169</v>
       </c>
       <c r="B57" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386784</v>
+        <v>386434</v>
       </c>
       <c r="R57" t="n">
-        <v>6758773</v>
+        <v>6758668</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6572,19 +6582,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6599,62 +6599,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131448283</v>
+        <v>131448293</v>
       </c>
       <c r="B58" t="n">
-        <v>57076</v>
+        <v>78916</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386456</v>
+        <v>386508</v>
       </c>
       <c r="R58" t="n">
-        <v>6758560</v>
+        <v>6758593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6686,7 +6681,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6696,7 +6691,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6723,56 +6718,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131440181</v>
+        <v>131448286</v>
       </c>
       <c r="B59" t="n">
-        <v>57076</v>
+        <v>78916</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386339</v>
+        <v>386475</v>
       </c>
       <c r="R59" t="n">
         <v>6758559</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6799,9 +6786,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6816,22 +6813,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131448293</v>
+        <v>131448312</v>
       </c>
       <c r="B60" t="n">
-        <v>78916</v>
+        <v>79869</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6839,21 +6836,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6863,10 +6860,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>386508</v>
+        <v>386410</v>
       </c>
       <c r="R60" t="n">
-        <v>6758593</v>
+        <v>6758596</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6898,7 +6895,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6908,7 +6905,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6935,10 +6932,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131448286</v>
+        <v>131448338</v>
       </c>
       <c r="B61" t="n">
-        <v>78916</v>
+        <v>79008</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6946,21 +6943,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6970,10 +6967,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>386475</v>
+        <v>386506</v>
       </c>
       <c r="R61" t="n">
-        <v>6758559</v>
+        <v>6758684</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7005,7 +7002,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7015,7 +7012,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7042,45 +7039,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131448312</v>
+        <v>131448283</v>
       </c>
       <c r="B62" t="n">
-        <v>79869</v>
+        <v>57076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386410</v>
+        <v>386456</v>
       </c>
       <c r="R62" t="n">
-        <v>6758596</v>
+        <v>6758560</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7112,7 +7114,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7122,7 +7124,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7149,48 +7151,56 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131448338</v>
+        <v>131440181</v>
       </c>
       <c r="B63" t="n">
-        <v>79008</v>
+        <v>57076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>386506</v>
+        <v>386339</v>
       </c>
       <c r="R63" t="n">
-        <v>6758684</v>
+        <v>6758559</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7217,19 +7227,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7244,12 +7244,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131440225</v>
+        <v>131448304</v>
       </c>
       <c r="B104" t="n">
-        <v>78916</v>
+        <v>79250</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11446,37 +11446,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>386426</v>
+        <v>386423</v>
       </c>
       <c r="R104" t="n">
-        <v>6758644</v>
+        <v>6758618</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11503,9 +11503,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11520,19 +11530,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131448399</v>
+        <v>131440217</v>
       </c>
       <c r="B105" t="n">
         <v>79250</v>
@@ -11563,17 +11573,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>386647</v>
+        <v>386476</v>
       </c>
       <c r="R105" t="n">
-        <v>6758685</v>
+        <v>6758669</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11600,19 +11610,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11627,22 +11627,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131448304</v>
+        <v>131440225</v>
       </c>
       <c r="B106" t="n">
-        <v>79250</v>
+        <v>78916</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11650,37 +11650,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>386423</v>
+        <v>386426</v>
       </c>
       <c r="R106" t="n">
-        <v>6758618</v>
+        <v>6758644</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11707,19 +11707,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11734,19 +11724,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131448337</v>
+        <v>131448399</v>
       </c>
       <c r="B107" t="n">
         <v>79250</v>
@@ -11781,10 +11771,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>386503</v>
+        <v>386647</v>
       </c>
       <c r="R107" t="n">
-        <v>6758670</v>
+        <v>6758685</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11816,7 +11806,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11826,7 +11816,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11853,7 +11843,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131440217</v>
+        <v>131448337</v>
       </c>
       <c r="B108" t="n">
         <v>79250</v>
@@ -11884,17 +11874,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>386476</v>
+        <v>386503</v>
       </c>
       <c r="R108" t="n">
-        <v>6758669</v>
+        <v>6758670</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11921,9 +11911,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11938,12 +11938,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131440184</v>
+        <v>131448402</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>78919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386349</v>
+        <v>386676</v>
       </c>
       <c r="R2" t="n">
-        <v>6758545</v>
+        <v>6758633</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +743,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,60 +770,68 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131448402</v>
+        <v>131440184</v>
       </c>
       <c r="B3" t="n">
-        <v>78916</v>
+        <v>57079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386676</v>
+        <v>386349</v>
       </c>
       <c r="R3" t="n">
-        <v>6758633</v>
+        <v>6758545</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,19 +858,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +875,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -890,7 +890,7 @@
         <v>131448361</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131448360</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>131448316</v>
       </c>
       <c r="B6" t="n">
-        <v>79274</v>
+        <v>79277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>131448307</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131448324</v>
+        <v>131448387</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>78919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386405</v>
+        <v>386707</v>
       </c>
       <c r="R8" t="n">
-        <v>6758668</v>
+        <v>6758689</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,48 +1422,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131440197</v>
+        <v>131448324</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386393</v>
+        <v>386405</v>
       </c>
       <c r="R9" t="n">
-        <v>6758564</v>
+        <v>6758668</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1490,40 +1490,49 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131448356</v>
+        <v>131440197</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>79277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,17 +1560,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386780</v>
+        <v>386393</v>
       </c>
       <c r="R10" t="n">
-        <v>6758712</v>
+        <v>6758564</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,49 +1597,40 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131440221</v>
+        <v>131448406</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,37 +1638,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386525</v>
+        <v>386719</v>
       </c>
       <c r="R11" t="n">
-        <v>6758695</v>
+        <v>6758587</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,9 +1695,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1712,44 +1722,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131448387</v>
+        <v>131448356</v>
       </c>
       <c r="B12" t="n">
-        <v>78916</v>
+        <v>79277</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386707</v>
+        <v>386780</v>
       </c>
       <c r="R12" t="n">
-        <v>6758689</v>
+        <v>6758712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,7 +1804,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1804,7 +1814,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,48 +1841,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131448406</v>
+        <v>131440187</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>57079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386719</v>
+        <v>386361</v>
       </c>
       <c r="R13" t="n">
-        <v>6758587</v>
+        <v>6758535</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1899,19 +1917,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1926,22 +1934,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131440187</v>
+        <v>131440186</v>
       </c>
       <c r="B14" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1981,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386361</v>
+        <v>386354</v>
       </c>
       <c r="R14" t="n">
-        <v>6758535</v>
+        <v>6758536</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2043,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131440186</v>
+        <v>131448319</v>
       </c>
       <c r="B15" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,27 +2080,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386354</v>
+        <v>386383</v>
       </c>
       <c r="R15" t="n">
-        <v>6758536</v>
+        <v>6758654</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2119,9 +2124,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,65 +2151,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131448319</v>
+        <v>131440221</v>
       </c>
       <c r="B16" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386383</v>
+        <v>386525</v>
       </c>
       <c r="R16" t="n">
-        <v>6758654</v>
+        <v>6758695</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2221,19 +2231,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,22 +2248,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448299</v>
+        <v>131448295</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386440</v>
+        <v>386474</v>
       </c>
       <c r="R17" t="n">
-        <v>6758599</v>
+        <v>6758587</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,48 +2367,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131448295</v>
+        <v>131440191</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386474</v>
+        <v>386397</v>
       </c>
       <c r="R18" t="n">
-        <v>6758587</v>
+        <v>6758574</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2435,19 +2443,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:32</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2462,22 +2460,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448375</v>
+        <v>131448350</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,21 +2483,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2507,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386743</v>
+        <v>386644</v>
       </c>
       <c r="R19" t="n">
-        <v>6758789</v>
+        <v>6758591</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2542,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2552,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448350</v>
+        <v>131448370</v>
       </c>
       <c r="B20" t="n">
-        <v>79008</v>
+        <v>79843</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2590,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386644</v>
+        <v>386751</v>
       </c>
       <c r="R20" t="n">
-        <v>6758591</v>
+        <v>6758793</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2649,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2659,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2686,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448370</v>
+        <v>131448344</v>
       </c>
       <c r="B21" t="n">
-        <v>79840</v>
+        <v>78919</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2697,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2721,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386751</v>
+        <v>386506</v>
       </c>
       <c r="R21" t="n">
-        <v>6758793</v>
+        <v>6758691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2756,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2768,7 +2766,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131440220</v>
+        <v>131448379</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>78919</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,37 +2804,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386519</v>
+        <v>386696</v>
       </c>
       <c r="R22" t="n">
-        <v>6758698</v>
+        <v>6758781</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2863,9 +2861,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2880,68 +2888,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131440191</v>
+        <v>131448363</v>
       </c>
       <c r="B23" t="n">
-        <v>57076</v>
+        <v>78919</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386397</v>
+        <v>386784</v>
       </c>
       <c r="R23" t="n">
-        <v>6758574</v>
+        <v>6758735</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2968,9 +2968,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2985,12 +2995,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3000,7 +3010,7 @@
         <v>131448259</v>
       </c>
       <c r="B24" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3104,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131448344</v>
+        <v>131440220</v>
       </c>
       <c r="B25" t="n">
-        <v>78916</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,37 +3125,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386506</v>
+        <v>386519</v>
       </c>
       <c r="R25" t="n">
-        <v>6758691</v>
+        <v>6758698</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3172,19 +3182,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3199,22 +3199,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448363</v>
+        <v>131448299</v>
       </c>
       <c r="B26" t="n">
-        <v>78916</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386784</v>
+        <v>386440</v>
       </c>
       <c r="R26" t="n">
-        <v>6758735</v>
+        <v>6758599</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131448379</v>
+        <v>131448375</v>
       </c>
       <c r="B27" t="n">
-        <v>78916</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386696</v>
+        <v>386743</v>
       </c>
       <c r="R27" t="n">
-        <v>6758781</v>
+        <v>6758789</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
         <v>131448292</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>131448368</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>131448409</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>131448327</v>
       </c>
       <c r="B31" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>131448386</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>131448329</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131448282</v>
+        <v>131440215</v>
       </c>
       <c r="B34" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,37 +4078,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386475</v>
+        <v>386402</v>
       </c>
       <c r="R34" t="n">
-        <v>6758559</v>
+        <v>6758574</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4135,19 +4135,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4162,22 +4152,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448382</v>
+        <v>131448282</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4185,21 +4175,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4199,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386718</v>
+        <v>386475</v>
       </c>
       <c r="R35" t="n">
-        <v>6758734</v>
+        <v>6758559</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4244,7 +4234,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4254,7 +4244,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4281,10 +4271,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131440215</v>
+        <v>131448382</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4312,17 +4302,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386402</v>
+        <v>386718</v>
       </c>
       <c r="R36" t="n">
-        <v>6758574</v>
+        <v>6758734</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4349,9 +4339,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,12 +4366,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
         <v>131440192</v>
       </c>
       <c r="B37" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4483,45 +4483,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131448347</v>
+        <v>131448321</v>
       </c>
       <c r="B38" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>386553</v>
+        <v>386394</v>
       </c>
       <c r="R38" t="n">
-        <v>6758704</v>
+        <v>6758643</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4553,7 +4558,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4563,7 +4568,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4590,10 +4595,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131448306</v>
+        <v>131448347</v>
       </c>
       <c r="B39" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4625,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>386428</v>
+        <v>386553</v>
       </c>
       <c r="R39" t="n">
-        <v>6758654</v>
+        <v>6758704</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4660,7 +4665,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4670,7 +4675,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4697,10 +4702,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131448352</v>
+        <v>131448306</v>
       </c>
       <c r="B40" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4708,21 +4713,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4732,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>386718</v>
+        <v>386428</v>
       </c>
       <c r="R40" t="n">
-        <v>6758619</v>
+        <v>6758654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4767,7 +4772,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4777,7 +4782,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4804,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131448396</v>
+        <v>131448352</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4815,21 +4820,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4839,10 +4844,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386635</v>
+        <v>386718</v>
       </c>
       <c r="R41" t="n">
-        <v>6758691</v>
+        <v>6758619</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4874,7 +4879,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4884,7 +4889,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4911,50 +4916,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448321</v>
+        <v>131448396</v>
       </c>
       <c r="B42" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386394</v>
+        <v>386635</v>
       </c>
       <c r="R42" t="n">
-        <v>6758643</v>
+        <v>6758691</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5026,7 +5026,7 @@
         <v>131448339</v>
       </c>
       <c r="B43" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5130,56 +5130,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131440180</v>
+        <v>131448403</v>
       </c>
       <c r="B44" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386351</v>
+        <v>386650</v>
       </c>
       <c r="R44" t="n">
-        <v>6758581</v>
+        <v>6758630</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5206,9 +5198,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5223,22 +5225,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448403</v>
+        <v>131448289</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5270,10 +5272,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386650</v>
+        <v>386519</v>
       </c>
       <c r="R45" t="n">
-        <v>6758630</v>
+        <v>6758591</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5305,7 +5307,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5315,7 +5317,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5342,10 +5344,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131448289</v>
+        <v>131440171</v>
       </c>
       <c r="B46" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5353,37 +5355,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>386519</v>
       </c>
       <c r="R46" t="n">
-        <v>6758591</v>
+        <v>6758682</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5410,19 +5412,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5437,22 +5429,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131440171</v>
+        <v>131448369</v>
       </c>
       <c r="B47" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5460,37 +5452,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386519</v>
+        <v>386774</v>
       </c>
       <c r="R47" t="n">
-        <v>6758682</v>
+        <v>6758809</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5517,9 +5509,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5534,22 +5536,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131448369</v>
+        <v>131448346</v>
       </c>
       <c r="B48" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5557,21 +5559,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5581,10 +5583,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386774</v>
+        <v>386558</v>
       </c>
       <c r="R48" t="n">
-        <v>6758809</v>
+        <v>6758731</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5616,7 +5618,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5626,7 +5628,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5653,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131448346</v>
+        <v>131448322</v>
       </c>
       <c r="B49" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5664,21 +5666,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5688,10 +5690,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386558</v>
+        <v>386380</v>
       </c>
       <c r="R49" t="n">
-        <v>6758731</v>
+        <v>6758666</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5723,7 +5725,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5733,7 +5735,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5760,48 +5762,56 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131448322</v>
+        <v>131440180</v>
       </c>
       <c r="B50" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386380</v>
+        <v>386351</v>
       </c>
       <c r="R50" t="n">
-        <v>6758666</v>
+        <v>6758581</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5828,19 +5838,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5855,62 +5855,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131448364</v>
+        <v>131448328</v>
       </c>
       <c r="B51" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386784</v>
+        <v>386450</v>
       </c>
       <c r="R51" t="n">
-        <v>6758773</v>
+        <v>6758649</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5942,7 +5937,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5952,7 +5947,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5979,10 +5974,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131448328</v>
+        <v>131448365</v>
       </c>
       <c r="B52" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6014,10 +6009,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386450</v>
+        <v>386808</v>
       </c>
       <c r="R52" t="n">
-        <v>6758649</v>
+        <v>6758791</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6049,7 +6044,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6059,7 +6054,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6086,10 +6081,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131448365</v>
+        <v>131448297</v>
       </c>
       <c r="B53" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6121,10 +6116,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>386808</v>
+        <v>386455</v>
       </c>
       <c r="R53" t="n">
-        <v>6758791</v>
+        <v>6758589</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6156,7 +6151,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6166,7 +6161,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6193,10 +6188,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448297</v>
+        <v>131448330</v>
       </c>
       <c r="B54" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6228,10 +6223,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386455</v>
+        <v>386474</v>
       </c>
       <c r="R54" t="n">
-        <v>6758589</v>
+        <v>6758628</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6263,7 +6258,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6273,7 +6268,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6300,10 +6295,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131448330</v>
+        <v>131448384</v>
       </c>
       <c r="B55" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6335,10 +6330,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386474</v>
+        <v>386721</v>
       </c>
       <c r="R55" t="n">
-        <v>6758628</v>
+        <v>6758722</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6370,7 +6365,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6380,7 +6375,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6407,10 +6402,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131448384</v>
+        <v>131440169</v>
       </c>
       <c r="B56" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6418,37 +6413,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386721</v>
+        <v>386434</v>
       </c>
       <c r="R56" t="n">
-        <v>6758722</v>
+        <v>6758668</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6475,19 +6470,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6502,60 +6487,65 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131440169</v>
+        <v>131448364</v>
       </c>
       <c r="B57" t="n">
-        <v>79869</v>
+        <v>57079</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386434</v>
+        <v>386784</v>
       </c>
       <c r="R57" t="n">
-        <v>6758668</v>
+        <v>6758773</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6582,9 +6572,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6599,12 +6599,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
         <v>131448293</v>
       </c>
       <c r="B58" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>131448286</v>
       </c>
       <c r="B59" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
         <v>131448312</v>
       </c>
       <c r="B60" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>131448338</v>
       </c>
       <c r="B61" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>131448283</v>
       </c>
       <c r="B62" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>131440181</v>
       </c>
       <c r="B63" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7256,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131448291</v>
+        <v>131448404</v>
       </c>
       <c r="B64" t="n">
-        <v>78916</v>
+        <v>79253</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7267,21 +7267,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>386519</v>
+        <v>386684</v>
       </c>
       <c r="R64" t="n">
-        <v>6758587</v>
+        <v>6758614</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7363,10 +7363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131448404</v>
+        <v>131440166</v>
       </c>
       <c r="B65" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7374,37 +7374,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>386684</v>
+        <v>386386</v>
       </c>
       <c r="R65" t="n">
-        <v>6758614</v>
+        <v>6758567</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7431,19 +7431,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7458,22 +7448,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131448318</v>
+        <v>131448381</v>
       </c>
       <c r="B66" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7505,10 +7495,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386391</v>
+        <v>386711</v>
       </c>
       <c r="R66" t="n">
-        <v>6758637</v>
+        <v>6758768</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7540,7 +7530,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7550,7 +7540,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7577,32 +7567,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131440166</v>
+        <v>131440204</v>
       </c>
       <c r="B67" t="n">
-        <v>79869</v>
+        <v>79277</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7612,10 +7602,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386386</v>
+        <v>386401</v>
       </c>
       <c r="R67" t="n">
-        <v>6758567</v>
+        <v>6758592</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7674,10 +7664,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131448381</v>
+        <v>131448281</v>
       </c>
       <c r="B68" t="n">
-        <v>79250</v>
+        <v>79010</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7685,21 +7675,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7709,10 +7699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386711</v>
+        <v>386443</v>
       </c>
       <c r="R68" t="n">
-        <v>6758768</v>
+        <v>6758546</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7744,7 +7734,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7754,7 +7744,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7781,10 +7771,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131440204</v>
+        <v>131448311</v>
       </c>
       <c r="B69" t="n">
-        <v>79274</v>
+        <v>57079</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7792,37 +7782,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>386401</v>
+        <v>386418</v>
       </c>
       <c r="R69" t="n">
-        <v>6758592</v>
+        <v>6758590</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7849,9 +7844,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7866,60 +7871,68 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131448323</v>
+        <v>131440185</v>
       </c>
       <c r="B70" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386418</v>
+        <v>386353</v>
       </c>
       <c r="R70" t="n">
-        <v>6758667</v>
+        <v>6758548</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7946,19 +7959,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7973,60 +7976,68 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131448366</v>
+        <v>131440179</v>
       </c>
       <c r="B71" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386800</v>
+        <v>386369</v>
       </c>
       <c r="R71" t="n">
-        <v>6758785</v>
+        <v>6758575</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8053,19 +8064,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8080,22 +8081,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131448281</v>
+        <v>131448291</v>
       </c>
       <c r="B72" t="n">
-        <v>79007</v>
+        <v>78919</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8103,21 +8104,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8127,10 +8128,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386443</v>
+        <v>386519</v>
       </c>
       <c r="R72" t="n">
-        <v>6758546</v>
+        <v>6758587</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8162,7 +8163,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8172,7 +8173,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8199,50 +8200,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131448311</v>
+        <v>131448318</v>
       </c>
       <c r="B73" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>386418</v>
+        <v>386391</v>
       </c>
       <c r="R73" t="n">
-        <v>6758590</v>
+        <v>6758637</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8274,7 +8270,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8284,7 +8280,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8311,56 +8307,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131440185</v>
+        <v>131448323</v>
       </c>
       <c r="B74" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386353</v>
+        <v>386418</v>
       </c>
       <c r="R74" t="n">
-        <v>6758548</v>
+        <v>6758667</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8387,9 +8375,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8404,68 +8402,60 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131440179</v>
+        <v>131448366</v>
       </c>
       <c r="B75" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386369</v>
+        <v>386800</v>
       </c>
       <c r="R75" t="n">
-        <v>6758575</v>
+        <v>6758785</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8492,9 +8482,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8509,12 +8509,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
         <v>131440152</v>
       </c>
       <c r="B76" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>131448317</v>
       </c>
       <c r="B77" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>131448372</v>
       </c>
       <c r="B78" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>131440168</v>
       </c>
       <c r="B79" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>131448280</v>
       </c>
       <c r="B80" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>131448341</v>
       </c>
       <c r="B81" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>131448314</v>
       </c>
       <c r="B82" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9256,48 +9256,56 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131448315</v>
+        <v>131440190</v>
       </c>
       <c r="B83" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
         <v>386402</v>
       </c>
       <c r="R83" t="n">
-        <v>6758596</v>
+        <v>6758572</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9324,19 +9332,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9351,22 +9349,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131448367</v>
+        <v>131440183</v>
       </c>
       <c r="B84" t="n">
-        <v>79274</v>
+        <v>57079</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9374,37 +9372,45 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>386774</v>
+        <v>386346</v>
       </c>
       <c r="R84" t="n">
-        <v>6758809</v>
+        <v>6758563</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9431,19 +9437,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9458,60 +9454,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131440172</v>
+        <v>131448367</v>
       </c>
       <c r="B85" t="n">
-        <v>79869</v>
+        <v>79277</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>386524</v>
+        <v>386774</v>
       </c>
       <c r="R85" t="n">
-        <v>6758661</v>
+        <v>6758809</v>
       </c>
       <c r="S85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9538,9 +9534,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9555,22 +9561,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131448343</v>
+        <v>131440172</v>
       </c>
       <c r="B86" t="n">
-        <v>79250</v>
+        <v>79872</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9578,37 +9584,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>386512</v>
+        <v>386524</v>
       </c>
       <c r="R86" t="n">
-        <v>6758697</v>
+        <v>6758661</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9635,19 +9641,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9662,60 +9658,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131440205</v>
+        <v>131448343</v>
       </c>
       <c r="B87" t="n">
-        <v>79274</v>
+        <v>79253</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>386413</v>
+        <v>386512</v>
       </c>
       <c r="R87" t="n">
-        <v>6758608</v>
+        <v>6758697</v>
       </c>
       <c r="S87" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9742,9 +9738,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9759,60 +9765,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131448362</v>
+        <v>131440205</v>
       </c>
       <c r="B88" t="n">
-        <v>79250</v>
+        <v>79277</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>386784</v>
+        <v>386413</v>
       </c>
       <c r="R88" t="n">
-        <v>6758735</v>
+        <v>6758608</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9839,19 +9845,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9866,22 +9862,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131448285</v>
+        <v>131448362</v>
       </c>
       <c r="B89" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9913,10 +9909,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>386496</v>
+        <v>386784</v>
       </c>
       <c r="R89" t="n">
-        <v>6758565</v>
+        <v>6758735</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9948,7 +9944,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9958,7 +9954,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9985,10 +9981,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131448359</v>
+        <v>131448285</v>
       </c>
       <c r="B90" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9996,21 +9992,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10020,10 +10016,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>386785</v>
+        <v>386496</v>
       </c>
       <c r="R90" t="n">
-        <v>6758750</v>
+        <v>6758565</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10055,7 +10051,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10065,7 +10061,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10092,56 +10088,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131440190</v>
+        <v>131448359</v>
       </c>
       <c r="B91" t="n">
-        <v>57076</v>
+        <v>79872</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>386402</v>
+        <v>386785</v>
       </c>
       <c r="R91" t="n">
-        <v>6758572</v>
+        <v>6758750</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10168,9 +10156,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10185,68 +10183,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131440183</v>
+        <v>131448315</v>
       </c>
       <c r="B92" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>386346</v>
+        <v>386402</v>
       </c>
       <c r="R92" t="n">
-        <v>6758563</v>
+        <v>6758596</v>
       </c>
       <c r="S92" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10273,9 +10263,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10290,12 +10290,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10305,7 +10305,7 @@
         <v>131448351</v>
       </c>
       <c r="B93" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>131440210</v>
       </c>
       <c r="B94" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>131448380</v>
       </c>
       <c r="B95" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>131440189</v>
       </c>
       <c r="B96" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10718,48 +10718,56 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131448284</v>
+        <v>131440188</v>
       </c>
       <c r="B97" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>386456</v>
+        <v>386381</v>
       </c>
       <c r="R97" t="n">
-        <v>6758560</v>
+        <v>6758531</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10786,19 +10794,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10813,22 +10811,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131440219</v>
+        <v>131448284</v>
       </c>
       <c r="B98" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10856,17 +10854,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>386495</v>
+        <v>386456</v>
       </c>
       <c r="R98" t="n">
-        <v>6758684</v>
+        <v>6758560</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10893,9 +10891,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10910,12 +10918,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10925,7 +10933,7 @@
         <v>131440170</v>
       </c>
       <c r="B99" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11022,7 +11030,7 @@
         <v>131448376</v>
       </c>
       <c r="B100" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11129,7 +11137,7 @@
         <v>131440216</v>
       </c>
       <c r="B101" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11226,7 +11234,7 @@
         <v>131448345</v>
       </c>
       <c r="B102" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11330,53 +11338,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131440188</v>
+        <v>131440219</v>
       </c>
       <c r="B103" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>386381</v>
+        <v>386495</v>
       </c>
       <c r="R103" t="n">
-        <v>6758531</v>
+        <v>6758684</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11435,10 +11435,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131448304</v>
+        <v>131440225</v>
       </c>
       <c r="B104" t="n">
-        <v>79250</v>
+        <v>78919</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11446,37 +11446,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>386423</v>
+        <v>386426</v>
       </c>
       <c r="R104" t="n">
-        <v>6758618</v>
+        <v>6758644</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11503,19 +11503,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:23</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11530,22 +11520,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131440217</v>
+        <v>131448399</v>
       </c>
       <c r="B105" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11573,17 +11563,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>386476</v>
+        <v>386647</v>
       </c>
       <c r="R105" t="n">
-        <v>6758669</v>
+        <v>6758685</v>
       </c>
       <c r="S105" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11610,9 +11600,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11627,22 +11627,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131440225</v>
+        <v>131448304</v>
       </c>
       <c r="B106" t="n">
-        <v>78916</v>
+        <v>79253</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11650,37 +11650,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>386426</v>
+        <v>386423</v>
       </c>
       <c r="R106" t="n">
-        <v>6758644</v>
+        <v>6758618</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11707,9 +11707,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11724,22 +11734,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131448399</v>
+        <v>131448337</v>
       </c>
       <c r="B107" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11771,10 +11781,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>386647</v>
+        <v>386503</v>
       </c>
       <c r="R107" t="n">
-        <v>6758685</v>
+        <v>6758670</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11806,7 +11816,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11816,7 +11826,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11843,10 +11853,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131448337</v>
+        <v>131440217</v>
       </c>
       <c r="B108" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11874,17 +11884,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>386503</v>
+        <v>386476</v>
       </c>
       <c r="R108" t="n">
-        <v>6758670</v>
+        <v>6758669</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11911,19 +11921,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11938,68 +11938,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131440182</v>
+        <v>131448401</v>
       </c>
       <c r="B109" t="n">
-        <v>57076</v>
+        <v>79253</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>386348</v>
+        <v>386677</v>
       </c>
       <c r="R109" t="n">
-        <v>6758562</v>
+        <v>6758630</v>
       </c>
       <c r="S109" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12026,9 +12018,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12043,22 +12045,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131448303</v>
+        <v>131440206</v>
       </c>
       <c r="B110" t="n">
-        <v>57076</v>
+        <v>79277</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12066,42 +12068,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>386417</v>
+        <v>386478</v>
       </c>
       <c r="R110" t="n">
-        <v>6758612</v>
+        <v>6758669</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12128,19 +12125,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12155,60 +12142,68 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131448401</v>
+        <v>131440182</v>
       </c>
       <c r="B111" t="n">
-        <v>79250</v>
+        <v>57079</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>386677</v>
+        <v>386348</v>
       </c>
       <c r="R111" t="n">
-        <v>6758630</v>
+        <v>6758562</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12235,19 +12230,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:51</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12262,22 +12247,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131440206</v>
+        <v>131448303</v>
       </c>
       <c r="B112" t="n">
-        <v>79274</v>
+        <v>57079</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12285,37 +12270,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>386478</v>
+        <v>386417</v>
       </c>
       <c r="R112" t="n">
-        <v>6758669</v>
+        <v>6758612</v>
       </c>
       <c r="S112" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12342,9 +12332,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12359,60 +12359,65 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131440224</v>
+        <v>131448287</v>
       </c>
       <c r="B113" t="n">
-        <v>78916</v>
+        <v>57079</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>386364</v>
+        <v>386516</v>
       </c>
       <c r="R113" t="n">
-        <v>6758576</v>
+        <v>6758592</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12439,9 +12444,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12456,65 +12471,60 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131448287</v>
+        <v>131440224</v>
       </c>
       <c r="B114" t="n">
-        <v>57076</v>
+        <v>78919</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>386516</v>
+        <v>386364</v>
       </c>
       <c r="R114" t="n">
-        <v>6758592</v>
+        <v>6758576</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12541,19 +12551,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12568,12 +12568,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -12583,7 +12583,7 @@
         <v>131448308</v>
       </c>
       <c r="B115" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>131448335</v>
       </c>
       <c r="B116" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12794,10 +12794,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131448374</v>
+        <v>131440167</v>
       </c>
       <c r="B117" t="n">
-        <v>78916</v>
+        <v>79872</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12805,37 +12805,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>386764</v>
+        <v>386367</v>
       </c>
       <c r="R117" t="n">
-        <v>6758806</v>
+        <v>6758574</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12862,19 +12862,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12889,22 +12879,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131440167</v>
+        <v>131448301</v>
       </c>
       <c r="B118" t="n">
-        <v>79869</v>
+        <v>79253</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12912,37 +12902,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>386367</v>
+        <v>386445</v>
       </c>
       <c r="R118" t="n">
-        <v>6758574</v>
+        <v>6758588</v>
       </c>
       <c r="S118" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12969,9 +12959,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12986,44 +12986,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131448301</v>
+        <v>131448383</v>
       </c>
       <c r="B119" t="n">
-        <v>79250</v>
+        <v>79277</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13033,10 +13033,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>386445</v>
+        <v>386711</v>
       </c>
       <c r="R119" t="n">
-        <v>6758588</v>
+        <v>6758695</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13105,32 +13105,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131448383</v>
+        <v>131448374</v>
       </c>
       <c r="B120" t="n">
-        <v>79274</v>
+        <v>78919</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>386711</v>
+        <v>386764</v>
       </c>
       <c r="R120" t="n">
-        <v>6758695</v>
+        <v>6758806</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13215,7 +13215,7 @@
         <v>131448268</v>
       </c>
       <c r="B121" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>131448320</v>
       </c>
       <c r="B122" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131448325</v>
+        <v>131448405</v>
       </c>
       <c r="B123" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>386431</v>
+        <v>386711</v>
       </c>
       <c r="R123" t="n">
-        <v>6758672</v>
+        <v>6758601</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13543,10 +13543,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131448405</v>
+        <v>131448325</v>
       </c>
       <c r="B124" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13578,10 +13578,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>386711</v>
+        <v>386431</v>
       </c>
       <c r="R124" t="n">
-        <v>6758601</v>
+        <v>6758672</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13613,7 +13613,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13653,7 +13653,7 @@
         <v>131448397</v>
       </c>
       <c r="B125" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>131448342</v>
       </c>
       <c r="B126" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131448402</v>
       </c>
       <c r="B2" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,56 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131440184</v>
+        <v>131448307</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386349</v>
+        <v>386416</v>
       </c>
       <c r="R3" t="n">
-        <v>6758545</v>
+        <v>6758577</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,9 +850,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,44 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448361</v>
+        <v>131448316</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386782</v>
+        <v>386346</v>
       </c>
       <c r="R4" t="n">
-        <v>6758744</v>
+        <v>6758614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -967,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,7 +999,7 @@
         <v>131448360</v>
       </c>
       <c r="B5" t="n">
-        <v>79277</v>
+        <v>79278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448316</v>
+        <v>131448361</v>
       </c>
       <c r="B6" t="n">
-        <v>79277</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386346</v>
+        <v>386782</v>
       </c>
       <c r="R6" t="n">
-        <v>6758614</v>
+        <v>6758744</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1181,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,48 +1210,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131448307</v>
+        <v>131440184</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386416</v>
+        <v>386349</v>
       </c>
       <c r="R7" t="n">
-        <v>6758577</v>
+        <v>6758545</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,19 +1286,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,60 +1303,68 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131448387</v>
+        <v>131440187</v>
       </c>
       <c r="B8" t="n">
-        <v>78919</v>
+        <v>57080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>386707</v>
+        <v>386361</v>
       </c>
       <c r="R8" t="n">
-        <v>6758689</v>
+        <v>6758535</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1383,19 +1391,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,22 +1408,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131448324</v>
+        <v>131448387</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>78920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386405</v>
+        <v>386707</v>
       </c>
       <c r="R9" t="n">
-        <v>6758668</v>
+        <v>6758689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1502,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,48 +1527,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131440197</v>
+        <v>131448406</v>
       </c>
       <c r="B10" t="n">
-        <v>79277</v>
+        <v>79873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386393</v>
+        <v>386719</v>
       </c>
       <c r="R10" t="n">
-        <v>6758564</v>
+        <v>6758587</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1597,40 +1595,49 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131448406</v>
+        <v>131440221</v>
       </c>
       <c r="B11" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,37 +1645,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386719</v>
+        <v>386525</v>
       </c>
       <c r="R11" t="n">
-        <v>6758587</v>
+        <v>6758695</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1695,19 +1702,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:46</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,44 +1719,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131448356</v>
+        <v>131448324</v>
       </c>
       <c r="B12" t="n">
-        <v>79277</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1769,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386780</v>
+        <v>386405</v>
       </c>
       <c r="R12" t="n">
-        <v>6758712</v>
+        <v>6758668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1801,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1814,7 +1811,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,10 +1838,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131440187</v>
+        <v>131448356</v>
       </c>
       <c r="B13" t="n">
-        <v>57079</v>
+        <v>79278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,45 +1849,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386361</v>
+        <v>386780</v>
       </c>
       <c r="R13" t="n">
-        <v>6758535</v>
+        <v>6758712</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1917,9 +1906,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,22 +1933,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131440186</v>
+        <v>131440197</v>
       </c>
       <c r="B14" t="n">
-        <v>57079</v>
+        <v>79278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,42 +1956,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386354</v>
+        <v>386393</v>
       </c>
       <c r="R14" t="n">
-        <v>6758536</v>
+        <v>6758564</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2033,6 +2024,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2051,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131448319</v>
+        <v>131440186</v>
       </c>
       <c r="B15" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2080,24 +2072,27 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386383</v>
+        <v>386354</v>
       </c>
       <c r="R15" t="n">
-        <v>6758654</v>
+        <v>6758536</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2124,19 +2119,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,60 +2136,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131440221</v>
+        <v>131448319</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386525</v>
+        <v>386383</v>
       </c>
       <c r="R16" t="n">
-        <v>6758695</v>
+        <v>6758654</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2231,9 +2221,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,22 +2248,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448295</v>
+        <v>131448259</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>78920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386474</v>
+        <v>386484</v>
       </c>
       <c r="R17" t="n">
-        <v>6758587</v>
+        <v>6758522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,56 +2367,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131440191</v>
+        <v>131448344</v>
       </c>
       <c r="B18" t="n">
-        <v>57079</v>
+        <v>78920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386397</v>
+        <v>386506</v>
       </c>
       <c r="R18" t="n">
-        <v>6758574</v>
+        <v>6758691</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2443,9 +2435,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2460,22 +2462,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448350</v>
+        <v>131448363</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>78920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2507,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386644</v>
+        <v>386784</v>
       </c>
       <c r="R19" t="n">
-        <v>6758591</v>
+        <v>6758735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2552,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2579,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448370</v>
+        <v>131448379</v>
       </c>
       <c r="B20" t="n">
-        <v>79843</v>
+        <v>78920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2590,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386751</v>
+        <v>386696</v>
       </c>
       <c r="R20" t="n">
-        <v>6758793</v>
+        <v>6758781</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2649,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2659,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448344</v>
+        <v>131448375</v>
       </c>
       <c r="B21" t="n">
-        <v>78919</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2697,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2721,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386506</v>
+        <v>386743</v>
       </c>
       <c r="R21" t="n">
-        <v>6758691</v>
+        <v>6758789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,7 +2758,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2766,7 +2768,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131448379</v>
+        <v>131448295</v>
       </c>
       <c r="B22" t="n">
-        <v>78919</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2828,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386696</v>
+        <v>386474</v>
       </c>
       <c r="R22" t="n">
-        <v>6758781</v>
+        <v>6758587</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,7 +2865,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2873,7 +2875,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2900,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131448363</v>
+        <v>131448299</v>
       </c>
       <c r="B23" t="n">
-        <v>78919</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2911,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2935,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386784</v>
+        <v>386440</v>
       </c>
       <c r="R23" t="n">
-        <v>6758735</v>
+        <v>6758599</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2970,7 +2972,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2980,7 +2982,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3007,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131448259</v>
+        <v>131440220</v>
       </c>
       <c r="B24" t="n">
-        <v>78919</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,37 +3020,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386484</v>
+        <v>386519</v>
       </c>
       <c r="R24" t="n">
-        <v>6758522</v>
+        <v>6758698</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3075,19 +3077,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3102,57 +3094,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131440220</v>
+        <v>131440191</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386519</v>
+        <v>386397</v>
       </c>
       <c r="R25" t="n">
-        <v>6758698</v>
+        <v>6758574</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448299</v>
+        <v>131448350</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386440</v>
+        <v>386644</v>
       </c>
       <c r="R26" t="n">
-        <v>6758599</v>
+        <v>6758591</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131448375</v>
+        <v>131448370</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79844</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386743</v>
+        <v>386751</v>
       </c>
       <c r="R27" t="n">
-        <v>6758789</v>
+        <v>6758793</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131448292</v>
+        <v>131448327</v>
       </c>
       <c r="B28" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386495</v>
+        <v>386449</v>
       </c>
       <c r="R28" t="n">
-        <v>6758597</v>
+        <v>6758648</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131448368</v>
+        <v>131448292</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>386787</v>
+        <v>386495</v>
       </c>
       <c r="R29" t="n">
-        <v>6758812</v>
+        <v>6758597</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3642,7 @@
         <v>131448409</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131448327</v>
+        <v>131448386</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>386449</v>
+        <v>386697</v>
       </c>
       <c r="R31" t="n">
-        <v>6758648</v>
+        <v>6758686</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131448386</v>
+        <v>131448329</v>
       </c>
       <c r="B32" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386697</v>
+        <v>386494</v>
       </c>
       <c r="R32" t="n">
-        <v>6758686</v>
+        <v>6758631</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3960,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131448329</v>
+        <v>131448368</v>
       </c>
       <c r="B33" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>386494</v>
+        <v>386787</v>
       </c>
       <c r="R33" t="n">
-        <v>6758631</v>
+        <v>6758812</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131440215</v>
+        <v>131448282</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4078,37 +4078,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>386402</v>
+        <v>386475</v>
       </c>
       <c r="R34" t="n">
-        <v>6758574</v>
+        <v>6758559</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4135,9 +4135,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4152,22 +4162,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131448282</v>
+        <v>131448382</v>
       </c>
       <c r="B35" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,21 +4185,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4199,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386475</v>
+        <v>386718</v>
       </c>
       <c r="R35" t="n">
-        <v>6758559</v>
+        <v>6758734</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4234,7 +4244,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4244,7 +4254,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4271,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131448382</v>
+        <v>131440215</v>
       </c>
       <c r="B36" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4302,17 +4312,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386718</v>
+        <v>386402</v>
       </c>
       <c r="R36" t="n">
-        <v>6758734</v>
+        <v>6758574</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4339,19 +4349,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,12 +4366,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
         <v>131440192</v>
       </c>
       <c r="B37" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4483,50 +4483,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131448321</v>
+        <v>131448306</v>
       </c>
       <c r="B38" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>386394</v>
+        <v>386428</v>
       </c>
       <c r="R38" t="n">
-        <v>6758643</v>
+        <v>6758654</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4558,7 +4553,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4568,7 +4563,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4595,10 +4590,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131448347</v>
+        <v>131448352</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4606,21 +4601,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4630,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>386553</v>
+        <v>386718</v>
       </c>
       <c r="R39" t="n">
-        <v>6758704</v>
+        <v>6758619</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4665,7 +4660,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4675,7 +4670,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4702,10 +4697,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131448306</v>
+        <v>131448396</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>386428</v>
+        <v>386635</v>
       </c>
       <c r="R40" t="n">
-        <v>6758654</v>
+        <v>6758691</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,7 +4767,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4782,7 +4777,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4809,10 +4804,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131448352</v>
+        <v>131448347</v>
       </c>
       <c r="B41" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4820,21 +4815,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4844,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386718</v>
+        <v>386553</v>
       </c>
       <c r="R41" t="n">
-        <v>6758619</v>
+        <v>6758704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,7 +4874,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4889,7 +4884,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4916,45 +4911,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131448396</v>
+        <v>131448321</v>
       </c>
       <c r="B42" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>386635</v>
+        <v>386394</v>
       </c>
       <c r="R42" t="n">
-        <v>6758691</v>
+        <v>6758643</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5026,7 +5026,7 @@
         <v>131448339</v>
       </c>
       <c r="B43" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131448403</v>
+        <v>131448369</v>
       </c>
       <c r="B44" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386650</v>
+        <v>386774</v>
       </c>
       <c r="R44" t="n">
-        <v>6758630</v>
+        <v>6758809</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5237,10 +5237,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131448289</v>
+        <v>131448346</v>
       </c>
       <c r="B45" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5248,21 +5248,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>386519</v>
+        <v>386558</v>
       </c>
       <c r="R45" t="n">
-        <v>6758591</v>
+        <v>6758731</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131440171</v>
+        <v>131448289</v>
       </c>
       <c r="B46" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5355,37 +5355,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>386519</v>
       </c>
       <c r="R46" t="n">
-        <v>6758682</v>
+        <v>6758591</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5412,9 +5412,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5429,22 +5439,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131448369</v>
+        <v>131448322</v>
       </c>
       <c r="B47" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5476,10 +5486,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>386774</v>
+        <v>386380</v>
       </c>
       <c r="R47" t="n">
-        <v>6758809</v>
+        <v>6758666</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5511,7 +5521,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5521,7 +5531,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5548,10 +5558,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131448346</v>
+        <v>131448403</v>
       </c>
       <c r="B48" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5559,21 +5569,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5583,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>386558</v>
+        <v>386650</v>
       </c>
       <c r="R48" t="n">
-        <v>6758731</v>
+        <v>6758630</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5618,7 +5628,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5628,7 +5638,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,10 +5665,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131448322</v>
+        <v>131440171</v>
       </c>
       <c r="B49" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5666,37 +5676,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>386380</v>
+        <v>386519</v>
       </c>
       <c r="R49" t="n">
-        <v>6758666</v>
+        <v>6758682</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5723,19 +5733,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5750,12 +5750,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
         <v>131440180</v>
       </c>
       <c r="B50" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5867,45 +5867,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131448328</v>
+        <v>131448364</v>
       </c>
       <c r="B51" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386450</v>
+        <v>386784</v>
       </c>
       <c r="R51" t="n">
-        <v>6758649</v>
+        <v>6758773</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5937,7 +5942,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5947,7 +5952,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5974,10 +5979,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131448365</v>
+        <v>131448384</v>
       </c>
       <c r="B52" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6009,10 +6014,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386808</v>
+        <v>386721</v>
       </c>
       <c r="R52" t="n">
-        <v>6758791</v>
+        <v>6758722</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6044,7 +6049,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6054,7 +6059,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6084,7 +6089,7 @@
         <v>131448297</v>
       </c>
       <c r="B53" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6188,10 +6193,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131448330</v>
+        <v>131448328</v>
       </c>
       <c r="B54" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6223,10 +6228,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386474</v>
+        <v>386450</v>
       </c>
       <c r="R54" t="n">
-        <v>6758628</v>
+        <v>6758649</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6258,7 +6263,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6268,7 +6273,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6295,10 +6300,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131448384</v>
+        <v>131448330</v>
       </c>
       <c r="B55" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6330,10 +6335,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>386721</v>
+        <v>386474</v>
       </c>
       <c r="R55" t="n">
-        <v>6758722</v>
+        <v>6758628</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6365,7 +6370,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6375,7 +6380,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6405,7 +6410,7 @@
         <v>131440169</v>
       </c>
       <c r="B56" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6499,50 +6504,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131448364</v>
+        <v>131448365</v>
       </c>
       <c r="B57" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386784</v>
+        <v>386808</v>
       </c>
       <c r="R57" t="n">
-        <v>6758773</v>
+        <v>6758791</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131448293</v>
+        <v>131448312</v>
       </c>
       <c r="B58" t="n">
-        <v>78919</v>
+        <v>79873</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386508</v>
+        <v>386410</v>
       </c>
       <c r="R58" t="n">
-        <v>6758593</v>
+        <v>6758596</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6718,10 +6718,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131448286</v>
+        <v>131448293</v>
       </c>
       <c r="B59" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386475</v>
+        <v>386508</v>
       </c>
       <c r="R59" t="n">
-        <v>6758559</v>
+        <v>6758593</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6825,10 +6825,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131448312</v>
+        <v>131448286</v>
       </c>
       <c r="B60" t="n">
-        <v>79872</v>
+        <v>78920</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6836,21 +6836,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>386410</v>
+        <v>386475</v>
       </c>
       <c r="R60" t="n">
-        <v>6758596</v>
+        <v>6758559</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6932,45 +6932,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131448338</v>
+        <v>131448283</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>57080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>386506</v>
+        <v>386456</v>
       </c>
       <c r="R61" t="n">
-        <v>6758684</v>
+        <v>6758560</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7002,7 +7007,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7012,7 +7017,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7039,10 +7044,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131448283</v>
+        <v>131440181</v>
       </c>
       <c r="B62" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7068,24 +7073,27 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386456</v>
+        <v>386339</v>
       </c>
       <c r="R62" t="n">
-        <v>6758560</v>
+        <v>6758559</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7112,19 +7120,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7139,68 +7137,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131440181</v>
+        <v>131448338</v>
       </c>
       <c r="B63" t="n">
-        <v>57079</v>
+        <v>79012</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>386339</v>
+        <v>386506</v>
       </c>
       <c r="R63" t="n">
-        <v>6758559</v>
+        <v>6758684</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7227,9 +7217,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7244,22 +7244,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131448404</v>
+        <v>131448323</v>
       </c>
       <c r="B64" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>386684</v>
+        <v>386418</v>
       </c>
       <c r="R64" t="n">
-        <v>6758614</v>
+        <v>6758667</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7363,10 +7363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131440166</v>
+        <v>131448381</v>
       </c>
       <c r="B65" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7374,37 +7374,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>386386</v>
+        <v>386711</v>
       </c>
       <c r="R65" t="n">
-        <v>6758567</v>
+        <v>6758768</v>
       </c>
       <c r="S65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7431,9 +7431,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7448,22 +7458,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131448381</v>
+        <v>131448366</v>
       </c>
       <c r="B66" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7495,10 +7505,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386711</v>
+        <v>386800</v>
       </c>
       <c r="R66" t="n">
-        <v>6758768</v>
+        <v>6758785</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7530,7 +7540,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7540,7 +7550,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7567,48 +7577,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131440204</v>
+        <v>131448281</v>
       </c>
       <c r="B67" t="n">
-        <v>79277</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386401</v>
+        <v>386443</v>
       </c>
       <c r="R67" t="n">
-        <v>6758592</v>
+        <v>6758546</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7635,9 +7645,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7652,22 +7672,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131448281</v>
+        <v>131448404</v>
       </c>
       <c r="B68" t="n">
-        <v>79010</v>
+        <v>79254</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7675,21 +7695,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7699,10 +7719,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386443</v>
+        <v>386684</v>
       </c>
       <c r="R68" t="n">
-        <v>6758546</v>
+        <v>6758614</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7734,7 +7754,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7744,7 +7764,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7771,10 +7791,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131448311</v>
+        <v>131440204</v>
       </c>
       <c r="B69" t="n">
-        <v>57079</v>
+        <v>79278</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7782,42 +7802,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>386418</v>
+        <v>386401</v>
       </c>
       <c r="R69" t="n">
-        <v>6758590</v>
+        <v>6758592</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7844,19 +7859,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7871,65 +7876,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131440185</v>
+        <v>131440166</v>
       </c>
       <c r="B70" t="n">
-        <v>57079</v>
+        <v>79873</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386353</v>
+        <v>386386</v>
       </c>
       <c r="R70" t="n">
-        <v>6758548</v>
+        <v>6758567</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7988,56 +7985,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131440179</v>
+        <v>131448318</v>
       </c>
       <c r="B71" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386369</v>
+        <v>386391</v>
       </c>
       <c r="R71" t="n">
-        <v>6758575</v>
+        <v>6758637</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8064,9 +8053,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8081,57 +8080,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131448291</v>
+        <v>131448311</v>
       </c>
       <c r="B72" t="n">
-        <v>78919</v>
+        <v>57080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386519</v>
+        <v>386418</v>
       </c>
       <c r="R72" t="n">
-        <v>6758587</v>
+        <v>6758590</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8163,7 +8167,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8173,7 +8177,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8200,48 +8204,56 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131448318</v>
+        <v>131440185</v>
       </c>
       <c r="B73" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>386391</v>
+        <v>386353</v>
       </c>
       <c r="R73" t="n">
-        <v>6758637</v>
+        <v>6758548</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8268,19 +8280,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8295,60 +8297,68 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131448323</v>
+        <v>131440179</v>
       </c>
       <c r="B74" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386418</v>
+        <v>386369</v>
       </c>
       <c r="R74" t="n">
-        <v>6758667</v>
+        <v>6758575</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8375,19 +8385,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8402,22 +8402,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131448366</v>
+        <v>131448291</v>
       </c>
       <c r="B75" t="n">
-        <v>79253</v>
+        <v>78920</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8425,21 +8425,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386800</v>
+        <v>386519</v>
       </c>
       <c r="R75" t="n">
-        <v>6758785</v>
+        <v>6758587</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8521,10 +8521,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131440152</v>
+        <v>131448280</v>
       </c>
       <c r="B76" t="n">
-        <v>79872</v>
+        <v>79012</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8532,37 +8532,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>386484</v>
+        <v>386443</v>
       </c>
       <c r="R76" t="n">
-        <v>6758687</v>
+        <v>6758546</v>
       </c>
       <c r="S76" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8589,40 +8589,49 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131448317</v>
+        <v>131440168</v>
       </c>
       <c r="B77" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8650,17 +8659,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386389</v>
+        <v>386357</v>
       </c>
       <c r="R77" t="n">
-        <v>6758642</v>
+        <v>6758539</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8687,19 +8696,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8714,12 +8713,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8729,7 +8728,7 @@
         <v>131448372</v>
       </c>
       <c r="B78" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8833,10 +8832,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131440168</v>
+        <v>131440152</v>
       </c>
       <c r="B79" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8868,10 +8867,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>386357</v>
+        <v>386484</v>
       </c>
       <c r="R79" t="n">
-        <v>6758539</v>
+        <v>6758687</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -8912,6 +8911,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8930,10 +8930,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131448280</v>
+        <v>131448317</v>
       </c>
       <c r="B80" t="n">
-        <v>79011</v>
+        <v>79873</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8941,21 +8941,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8965,10 +8965,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>386443</v>
+        <v>386389</v>
       </c>
       <c r="R80" t="n">
-        <v>6758546</v>
+        <v>6758642</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9040,7 +9040,7 @@
         <v>131448341</v>
       </c>
       <c r="B81" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>131448314</v>
       </c>
       <c r="B82" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9256,53 +9256,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131440190</v>
+        <v>131440172</v>
       </c>
       <c r="B83" t="n">
-        <v>57079</v>
+        <v>79873</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>386402</v>
+        <v>386524</v>
       </c>
       <c r="R83" t="n">
-        <v>6758572</v>
+        <v>6758661</v>
       </c>
       <c r="S83" t="n">
         <v>20</v>
@@ -9361,56 +9353,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131440183</v>
+        <v>131448315</v>
       </c>
       <c r="B84" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>386346</v>
+        <v>386402</v>
       </c>
       <c r="R84" t="n">
-        <v>6758563</v>
+        <v>6758596</v>
       </c>
       <c r="S84" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9437,9 +9421,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9454,44 +9448,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131448367</v>
+        <v>131448362</v>
       </c>
       <c r="B85" t="n">
-        <v>79277</v>
+        <v>79254</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9501,10 +9495,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>386774</v>
+        <v>386784</v>
       </c>
       <c r="R85" t="n">
-        <v>6758809</v>
+        <v>6758735</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9536,7 +9530,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9546,7 +9540,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9573,10 +9567,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131440172</v>
+        <v>131448285</v>
       </c>
       <c r="B86" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9584,37 +9578,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>386524</v>
+        <v>386496</v>
       </c>
       <c r="R86" t="n">
-        <v>6758661</v>
+        <v>6758565</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9641,9 +9635,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9658,44 +9662,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131448343</v>
+        <v>131448367</v>
       </c>
       <c r="B87" t="n">
-        <v>79253</v>
+        <v>79278</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9705,10 +9709,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>386512</v>
+        <v>386774</v>
       </c>
       <c r="R87" t="n">
-        <v>6758697</v>
+        <v>6758809</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9740,7 +9744,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9750,7 +9754,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9777,48 +9781,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131440205</v>
+        <v>131448359</v>
       </c>
       <c r="B88" t="n">
-        <v>79277</v>
+        <v>79873</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>386413</v>
+        <v>386785</v>
       </c>
       <c r="R88" t="n">
-        <v>6758608</v>
+        <v>6758750</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9845,9 +9849,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9862,60 +9876,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131448362</v>
+        <v>131440205</v>
       </c>
       <c r="B89" t="n">
-        <v>79253</v>
+        <v>79278</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>386784</v>
+        <v>386413</v>
       </c>
       <c r="R89" t="n">
-        <v>6758735</v>
+        <v>6758608</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9942,19 +9956,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9969,22 +9973,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131448285</v>
+        <v>131448343</v>
       </c>
       <c r="B90" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10016,10 +10020,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>386496</v>
+        <v>386512</v>
       </c>
       <c r="R90" t="n">
-        <v>6758565</v>
+        <v>6758697</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10051,7 +10055,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10061,7 +10065,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10088,48 +10092,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131448359</v>
+        <v>131440190</v>
       </c>
       <c r="B91" t="n">
-        <v>79872</v>
+        <v>57080</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>386785</v>
+        <v>386402</v>
       </c>
       <c r="R91" t="n">
-        <v>6758750</v>
+        <v>6758572</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10156,19 +10168,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10183,60 +10185,68 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131448315</v>
+        <v>131440183</v>
       </c>
       <c r="B92" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>386402</v>
+        <v>386346</v>
       </c>
       <c r="R92" t="n">
-        <v>6758596</v>
+        <v>6758563</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10263,19 +10273,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10290,22 +10290,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131448351</v>
+        <v>131440210</v>
       </c>
       <c r="B93" t="n">
-        <v>79253</v>
+        <v>79011</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10313,37 +10313,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>386637</v>
+        <v>386347</v>
       </c>
       <c r="R93" t="n">
-        <v>6758584</v>
+        <v>6758542</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10370,19 +10370,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10397,22 +10387,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131440210</v>
+        <v>131448351</v>
       </c>
       <c r="B94" t="n">
-        <v>79010</v>
+        <v>79254</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10420,37 +10410,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>386347</v>
+        <v>386637</v>
       </c>
       <c r="R94" t="n">
-        <v>6758542</v>
+        <v>6758584</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10477,9 +10467,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10494,12 +10494,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10509,7 +10509,7 @@
         <v>131448380</v>
       </c>
       <c r="B95" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>131440189</v>
       </c>
       <c r="B96" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10718,53 +10718,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131440188</v>
+        <v>131440219</v>
       </c>
       <c r="B97" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>386381</v>
+        <v>386495</v>
       </c>
       <c r="R97" t="n">
-        <v>6758531</v>
+        <v>6758684</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10823,10 +10815,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131448284</v>
+        <v>131448345</v>
       </c>
       <c r="B98" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10858,10 +10850,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>386456</v>
+        <v>386536</v>
       </c>
       <c r="R98" t="n">
-        <v>6758560</v>
+        <v>6758715</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10893,7 +10885,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10903,7 +10895,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10930,10 +10922,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131440170</v>
+        <v>131448376</v>
       </c>
       <c r="B99" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10941,37 +10933,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>386518</v>
+        <v>386715</v>
       </c>
       <c r="R99" t="n">
-        <v>6758680</v>
+        <v>6758795</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10998,9 +10990,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11015,22 +11017,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131448376</v>
+        <v>131448284</v>
       </c>
       <c r="B100" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11062,10 +11064,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>386715</v>
+        <v>386456</v>
       </c>
       <c r="R100" t="n">
-        <v>6758795</v>
+        <v>6758560</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11097,7 +11099,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11107,7 +11109,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11137,7 +11139,7 @@
         <v>131440216</v>
       </c>
       <c r="B101" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11231,10 +11233,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131448345</v>
+        <v>131440170</v>
       </c>
       <c r="B102" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11242,37 +11244,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>386536</v>
+        <v>386518</v>
       </c>
       <c r="R102" t="n">
-        <v>6758715</v>
+        <v>6758680</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11299,19 +11301,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11326,57 +11318,65 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131440219</v>
+        <v>131440188</v>
       </c>
       <c r="B103" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>386495</v>
+        <v>386381</v>
       </c>
       <c r="R103" t="n">
-        <v>6758684</v>
+        <v>6758531</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -11438,7 +11438,7 @@
         <v>131440225</v>
       </c>
       <c r="B104" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11532,10 +11532,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131448399</v>
+        <v>131448337</v>
       </c>
       <c r="B105" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>386647</v>
+        <v>386503</v>
       </c>
       <c r="R105" t="n">
-        <v>6758685</v>
+        <v>6758670</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11639,10 +11639,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131448304</v>
+        <v>131448399</v>
       </c>
       <c r="B106" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11674,10 +11674,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>386423</v>
+        <v>386647</v>
       </c>
       <c r="R106" t="n">
-        <v>6758618</v>
+        <v>6758685</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11746,10 +11746,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131448337</v>
+        <v>131440217</v>
       </c>
       <c r="B107" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11777,17 +11777,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>386503</v>
+        <v>386476</v>
       </c>
       <c r="R107" t="n">
-        <v>6758670</v>
+        <v>6758669</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11814,19 +11814,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11841,22 +11831,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131440217</v>
+        <v>131448304</v>
       </c>
       <c r="B108" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11884,17 +11874,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>386476</v>
+        <v>386423</v>
       </c>
       <c r="R108" t="n">
-        <v>6758669</v>
+        <v>6758618</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11921,9 +11911,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11938,12 +11938,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11953,7 +11953,7 @@
         <v>131448401</v>
       </c>
       <c r="B109" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>131440206</v>
       </c>
       <c r="B110" t="n">
-        <v>79277</v>
+        <v>79278</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>131440182</v>
       </c>
       <c r="B111" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>131448303</v>
       </c>
       <c r="B112" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12371,53 +12371,48 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131448287</v>
+        <v>131440224</v>
       </c>
       <c r="B113" t="n">
-        <v>57079</v>
+        <v>78920</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>386516</v>
+        <v>386364</v>
       </c>
       <c r="R113" t="n">
-        <v>6758592</v>
+        <v>6758576</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12444,19 +12439,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12471,22 +12456,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131440224</v>
+        <v>131448308</v>
       </c>
       <c r="B114" t="n">
-        <v>78919</v>
+        <v>79873</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12494,37 +12479,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>386364</v>
+        <v>386413</v>
       </c>
       <c r="R114" t="n">
-        <v>6758576</v>
+        <v>6758591</v>
       </c>
       <c r="S114" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12551,9 +12536,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12568,22 +12563,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131448308</v>
+        <v>131448335</v>
       </c>
       <c r="B115" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12591,21 +12586,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12615,10 +12610,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>386413</v>
+        <v>386526</v>
       </c>
       <c r="R115" t="n">
-        <v>6758591</v>
+        <v>6758655</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12650,7 +12645,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12660,7 +12655,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12687,45 +12682,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131448335</v>
+        <v>131448287</v>
       </c>
       <c r="B116" t="n">
-        <v>79253</v>
+        <v>57080</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>386526</v>
+        <v>386516</v>
       </c>
       <c r="R116" t="n">
-        <v>6758655</v>
+        <v>6758592</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12794,10 +12794,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131440167</v>
+        <v>131448374</v>
       </c>
       <c r="B117" t="n">
-        <v>79872</v>
+        <v>78920</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12805,37 +12805,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>386367</v>
+        <v>386764</v>
       </c>
       <c r="R117" t="n">
-        <v>6758574</v>
+        <v>6758806</v>
       </c>
       <c r="S117" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12862,9 +12862,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12879,44 +12889,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131448301</v>
+        <v>131448383</v>
       </c>
       <c r="B118" t="n">
-        <v>79253</v>
+        <v>79278</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12926,10 +12936,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>386445</v>
+        <v>386711</v>
       </c>
       <c r="R118" t="n">
-        <v>6758588</v>
+        <v>6758695</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12961,7 +12971,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12971,7 +12981,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12998,10 +13008,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131448383</v>
+        <v>131448268</v>
       </c>
       <c r="B119" t="n">
-        <v>79277</v>
+        <v>57080</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13009,34 +13019,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>386711</v>
+        <v>386348</v>
       </c>
       <c r="R119" t="n">
-        <v>6758695</v>
+        <v>6758527</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13068,7 +13083,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13078,7 +13093,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13105,45 +13120,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131448374</v>
+        <v>131448320</v>
       </c>
       <c r="B120" t="n">
-        <v>78919</v>
+        <v>57080</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>386764</v>
+        <v>386392</v>
       </c>
       <c r="R120" t="n">
-        <v>6758806</v>
+        <v>6758650</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13175,7 +13195,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13185,7 +13205,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13212,53 +13232,48 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131448268</v>
+        <v>131440167</v>
       </c>
       <c r="B121" t="n">
-        <v>57079</v>
+        <v>79873</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>386348</v>
+        <v>386367</v>
       </c>
       <c r="R121" t="n">
-        <v>6758527</v>
+        <v>6758574</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13285,19 +13300,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13312,62 +13317,57 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131448320</v>
+        <v>131448301</v>
       </c>
       <c r="B122" t="n">
-        <v>57079</v>
+        <v>79254</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>386392</v>
+        <v>386445</v>
       </c>
       <c r="R122" t="n">
-        <v>6758650</v>
+        <v>6758588</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13436,10 +13436,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>131448405</v>
+        <v>131448325</v>
       </c>
       <c r="B123" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13471,10 +13471,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>386711</v>
+        <v>386431</v>
       </c>
       <c r="R123" t="n">
-        <v>6758601</v>
+        <v>6758672</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13543,10 +13543,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>131448325</v>
+        <v>131448405</v>
       </c>
       <c r="B124" t="n">
-        <v>78919</v>
+        <v>78920</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13578,10 +13578,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>386431</v>
+        <v>386711</v>
       </c>
       <c r="R124" t="n">
-        <v>6758672</v>
+        <v>6758601</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13613,7 +13613,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13650,10 +13650,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131448397</v>
+        <v>131448342</v>
       </c>
       <c r="B125" t="n">
-        <v>79253</v>
+        <v>79873</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13661,21 +13661,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13685,10 +13685,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>386638</v>
+        <v>386512</v>
       </c>
       <c r="R125" t="n">
-        <v>6758692</v>
+        <v>6758697</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13757,10 +13757,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131448342</v>
+        <v>131448397</v>
       </c>
       <c r="B126" t="n">
-        <v>79872</v>
+        <v>79254</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13768,21 +13768,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13792,10 +13792,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>386512</v>
+        <v>386638</v>
       </c>
       <c r="R126" t="n">
-        <v>6758697</v>
+        <v>6758692</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -782,48 +782,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131448307</v>
+        <v>131440184</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386416</v>
+        <v>386349</v>
       </c>
       <c r="R3" t="n">
-        <v>6758577</v>
+        <v>6758545</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +858,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +875,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131448316</v>
+        <v>131448307</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>386346</v>
+        <v>386416</v>
       </c>
       <c r="R4" t="n">
-        <v>6758614</v>
+        <v>6758577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +957,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +967,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131448360</v>
+        <v>131448316</v>
       </c>
       <c r="B5" t="n">
         <v>79278</v>
@@ -1031,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>386785</v>
+        <v>386346</v>
       </c>
       <c r="R5" t="n">
-        <v>6758750</v>
+        <v>6758614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1064,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1074,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1101,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131448361</v>
+        <v>131448360</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>386782</v>
+        <v>386785</v>
       </c>
       <c r="R6" t="n">
-        <v>6758744</v>
+        <v>6758750</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,56 +1208,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131440184</v>
+        <v>131448361</v>
       </c>
       <c r="B7" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>386349</v>
+        <v>386782</v>
       </c>
       <c r="R7" t="n">
-        <v>6758545</v>
+        <v>6758744</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1286,9 +1276,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,12 +1303,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1420,48 +1420,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131448387</v>
+        <v>131440186</v>
       </c>
       <c r="B9" t="n">
-        <v>78920</v>
+        <v>57080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>386707</v>
+        <v>386354</v>
       </c>
       <c r="R9" t="n">
-        <v>6758689</v>
+        <v>6758536</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,19 +1496,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,57 +1513,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131448406</v>
+        <v>131448319</v>
       </c>
       <c r="B10" t="n">
-        <v>79873</v>
+        <v>57080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>386719</v>
+        <v>386383</v>
       </c>
       <c r="R10" t="n">
-        <v>6758587</v>
+        <v>6758654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,7 +1600,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1610,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131440221</v>
+        <v>131448387</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>78920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,37 +1648,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>386525</v>
+        <v>386707</v>
       </c>
       <c r="R11" t="n">
-        <v>6758695</v>
+        <v>6758689</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1702,9 +1705,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,22 +1732,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131448324</v>
+        <v>131448406</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1766,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>386405</v>
+        <v>386719</v>
       </c>
       <c r="R12" t="n">
-        <v>6758668</v>
+        <v>6758587</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,7 +1814,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1811,7 +1824,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,48 +1851,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131448356</v>
+        <v>131440221</v>
       </c>
       <c r="B13" t="n">
-        <v>79278</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>386780</v>
+        <v>386525</v>
       </c>
       <c r="R13" t="n">
-        <v>6758712</v>
+        <v>6758695</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1906,19 +1919,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,60 +1936,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131440197</v>
+        <v>131448324</v>
       </c>
       <c r="B14" t="n">
-        <v>79278</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>386393</v>
+        <v>386405</v>
       </c>
       <c r="R14" t="n">
-        <v>6758564</v>
+        <v>6758668</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2013,40 +2016,49 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131440186</v>
+        <v>131448356</v>
       </c>
       <c r="B15" t="n">
-        <v>57080</v>
+        <v>79278</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2054,45 +2066,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>386354</v>
+        <v>386780</v>
       </c>
       <c r="R15" t="n">
-        <v>6758536</v>
+        <v>6758712</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2119,9 +2123,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,22 +2150,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131448319</v>
+        <v>131440197</v>
       </c>
       <c r="B16" t="n">
-        <v>57080</v>
+        <v>79278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,42 +2173,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386383</v>
+        <v>386393</v>
       </c>
       <c r="R16" t="n">
-        <v>6758654</v>
+        <v>6758564</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2221,49 +2230,40 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131448259</v>
+        <v>131448350</v>
       </c>
       <c r="B17" t="n">
-        <v>78920</v>
+        <v>79012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386484</v>
+        <v>386644</v>
       </c>
       <c r="R17" t="n">
-        <v>6758522</v>
+        <v>6758591</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131448344</v>
+        <v>131448370</v>
       </c>
       <c r="B18" t="n">
-        <v>78920</v>
+        <v>79844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>386506</v>
+        <v>386751</v>
       </c>
       <c r="R18" t="n">
-        <v>6758691</v>
+        <v>6758793</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131448363</v>
+        <v>131448259</v>
       </c>
       <c r="B19" t="n">
         <v>78920</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>386784</v>
+        <v>386484</v>
       </c>
       <c r="R19" t="n">
-        <v>6758735</v>
+        <v>6758522</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131448379</v>
+        <v>131448344</v>
       </c>
       <c r="B20" t="n">
         <v>78920</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>386696</v>
+        <v>386506</v>
       </c>
       <c r="R20" t="n">
-        <v>6758781</v>
+        <v>6758691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131448375</v>
+        <v>131448363</v>
       </c>
       <c r="B21" t="n">
-        <v>79254</v>
+        <v>78920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386743</v>
+        <v>386784</v>
       </c>
       <c r="R21" t="n">
-        <v>6758789</v>
+        <v>6758735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131448295</v>
+        <v>131448379</v>
       </c>
       <c r="B22" t="n">
-        <v>79254</v>
+        <v>78920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>386474</v>
+        <v>386696</v>
       </c>
       <c r="R22" t="n">
-        <v>6758587</v>
+        <v>6758781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,7 +2902,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131448299</v>
+        <v>131440220</v>
       </c>
       <c r="B23" t="n">
         <v>79254</v>
@@ -2933,17 +2933,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>386440</v>
+        <v>386519</v>
       </c>
       <c r="R23" t="n">
-        <v>6758599</v>
+        <v>6758698</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2970,19 +2970,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,57 +2987,65 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131440220</v>
+        <v>131440191</v>
       </c>
       <c r="B24" t="n">
-        <v>79254</v>
+        <v>57080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>386519</v>
+        <v>386397</v>
       </c>
       <c r="R24" t="n">
-        <v>6758698</v>
+        <v>6758574</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3106,56 +3104,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131440191</v>
+        <v>131448375</v>
       </c>
       <c r="B25" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386397</v>
+        <v>386743</v>
       </c>
       <c r="R25" t="n">
-        <v>6758574</v>
+        <v>6758789</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3182,9 +3172,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3199,22 +3199,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131448350</v>
+        <v>131448295</v>
       </c>
       <c r="B26" t="n">
-        <v>79012</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386644</v>
+        <v>386474</v>
       </c>
       <c r="R26" t="n">
-        <v>6758591</v>
+        <v>6758587</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131448370</v>
+        <v>131448299</v>
       </c>
       <c r="B27" t="n">
-        <v>79844</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,21 +3329,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>386751</v>
+        <v>386440</v>
       </c>
       <c r="R27" t="n">
-        <v>6758793</v>
+        <v>6758599</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131448312</v>
+        <v>131448293</v>
       </c>
       <c r="B58" t="n">
-        <v>79873</v>
+        <v>78920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386410</v>
+        <v>386508</v>
       </c>
       <c r="R58" t="n">
-        <v>6758596</v>
+        <v>6758593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6718,7 +6718,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131448293</v>
+        <v>131448286</v>
       </c>
       <c r="B59" t="n">
         <v>78920</v>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386508</v>
+        <v>386475</v>
       </c>
       <c r="R59" t="n">
-        <v>6758593</v>
+        <v>6758559</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6825,10 +6825,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131448286</v>
+        <v>131448312</v>
       </c>
       <c r="B60" t="n">
-        <v>78920</v>
+        <v>79873</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6836,21 +6836,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>386475</v>
+        <v>386410</v>
       </c>
       <c r="R60" t="n">
-        <v>6758559</v>
+        <v>6758596</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6905,7 +6905,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7256,10 +7256,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131448323</v>
+        <v>131448291</v>
       </c>
       <c r="B64" t="n">
-        <v>79254</v>
+        <v>78920</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7267,21 +7267,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>386418</v>
+        <v>386519</v>
       </c>
       <c r="R64" t="n">
-        <v>6758667</v>
+        <v>6758587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7363,7 +7363,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131448381</v>
+        <v>131448323</v>
       </c>
       <c r="B65" t="n">
         <v>79254</v>
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>386711</v>
+        <v>386418</v>
       </c>
       <c r="R65" t="n">
-        <v>6758768</v>
+        <v>6758667</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7470,7 +7470,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131448366</v>
+        <v>131448381</v>
       </c>
       <c r="B66" t="n">
         <v>79254</v>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386800</v>
+        <v>386711</v>
       </c>
       <c r="R66" t="n">
-        <v>6758785</v>
+        <v>6758768</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7577,10 +7577,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131448281</v>
+        <v>131448366</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>79254</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7588,21 +7588,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386443</v>
+        <v>386800</v>
       </c>
       <c r="R67" t="n">
-        <v>6758546</v>
+        <v>6758785</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7684,10 +7684,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131448404</v>
+        <v>131448281</v>
       </c>
       <c r="B68" t="n">
-        <v>79254</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7695,21 +7695,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7719,10 +7719,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386684</v>
+        <v>386443</v>
       </c>
       <c r="R68" t="n">
-        <v>6758614</v>
+        <v>6758546</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7791,48 +7791,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131440204</v>
+        <v>131448404</v>
       </c>
       <c r="B69" t="n">
-        <v>79278</v>
+        <v>79254</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>386401</v>
+        <v>386684</v>
       </c>
       <c r="R69" t="n">
-        <v>6758592</v>
+        <v>6758614</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7859,9 +7859,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7876,44 +7886,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131440166</v>
+        <v>131440204</v>
       </c>
       <c r="B70" t="n">
-        <v>79873</v>
+        <v>79278</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7923,10 +7933,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386386</v>
+        <v>386401</v>
       </c>
       <c r="R70" t="n">
-        <v>6758567</v>
+        <v>6758592</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -7985,10 +7995,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131448318</v>
+        <v>131440166</v>
       </c>
       <c r="B71" t="n">
-        <v>79254</v>
+        <v>79873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7996,37 +8006,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386391</v>
+        <v>386386</v>
       </c>
       <c r="R71" t="n">
-        <v>6758637</v>
+        <v>6758567</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8053,19 +8063,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>12:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8080,62 +8080,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131448311</v>
+        <v>131448318</v>
       </c>
       <c r="B72" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386418</v>
+        <v>386391</v>
       </c>
       <c r="R72" t="n">
-        <v>6758590</v>
+        <v>6758637</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8167,7 +8162,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8177,7 +8172,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8204,7 +8199,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131440185</v>
+        <v>131448311</v>
       </c>
       <c r="B73" t="n">
         <v>57080</v>
@@ -8233,27 +8228,24 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>386353</v>
+        <v>386418</v>
       </c>
       <c r="R73" t="n">
-        <v>6758548</v>
+        <v>6758590</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8280,9 +8272,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8297,19 +8299,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131440179</v>
+        <v>131440185</v>
       </c>
       <c r="B74" t="n">
         <v>57080</v>
@@ -8352,10 +8354,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386369</v>
+        <v>386353</v>
       </c>
       <c r="R74" t="n">
-        <v>6758575</v>
+        <v>6758548</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8414,48 +8416,56 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131448291</v>
+        <v>131440179</v>
       </c>
       <c r="B75" t="n">
-        <v>78920</v>
+        <v>57080</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386519</v>
+        <v>386369</v>
       </c>
       <c r="R75" t="n">
-        <v>6758587</v>
+        <v>6758575</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8482,19 +8492,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8509,12 +8509,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -10718,45 +10718,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131440219</v>
+        <v>131440188</v>
       </c>
       <c r="B97" t="n">
-        <v>79254</v>
+        <v>57080</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>386495</v>
+        <v>386381</v>
       </c>
       <c r="R97" t="n">
-        <v>6758684</v>
+        <v>6758531</v>
       </c>
       <c r="S97" t="n">
         <v>20</v>
@@ -10815,7 +10823,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131448345</v>
+        <v>131440219</v>
       </c>
       <c r="B98" t="n">
         <v>79254</v>
@@ -10846,17 +10854,17 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>386536</v>
+        <v>386495</v>
       </c>
       <c r="R98" t="n">
-        <v>6758715</v>
+        <v>6758684</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10883,19 +10891,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10910,19 +10908,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131448376</v>
+        <v>131448345</v>
       </c>
       <c r="B99" t="n">
         <v>79254</v>
@@ -10957,10 +10955,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>386715</v>
+        <v>386536</v>
       </c>
       <c r="R99" t="n">
-        <v>6758795</v>
+        <v>6758715</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10992,7 +10990,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11002,7 +11000,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11029,7 +11027,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131448284</v>
+        <v>131448376</v>
       </c>
       <c r="B100" t="n">
         <v>79254</v>
@@ -11064,10 +11062,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>386456</v>
+        <v>386715</v>
       </c>
       <c r="R100" t="n">
-        <v>6758560</v>
+        <v>6758795</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11099,7 +11097,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11109,7 +11107,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11136,7 +11134,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131440216</v>
+        <v>131448284</v>
       </c>
       <c r="B101" t="n">
         <v>79254</v>
@@ -11167,17 +11165,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>386401</v>
+        <v>386456</v>
       </c>
       <c r="R101" t="n">
-        <v>6758591</v>
+        <v>6758560</v>
       </c>
       <c r="S101" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11204,9 +11202,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11221,22 +11229,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131440170</v>
+        <v>131440216</v>
       </c>
       <c r="B102" t="n">
-        <v>79873</v>
+        <v>79254</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11244,21 +11252,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11268,10 +11276,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>386518</v>
+        <v>386401</v>
       </c>
       <c r="R102" t="n">
-        <v>6758680</v>
+        <v>6758591</v>
       </c>
       <c r="S102" t="n">
         <v>20</v>
@@ -11330,53 +11338,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131440188</v>
+        <v>131440170</v>
       </c>
       <c r="B103" t="n">
-        <v>57080</v>
+        <v>79873</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>386381</v>
+        <v>386518</v>
       </c>
       <c r="R103" t="n">
-        <v>6758531</v>
+        <v>6758680</v>
       </c>
       <c r="S103" t="n">
         <v>20</v>
@@ -12371,48 +12371,53 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131440224</v>
+        <v>131448287</v>
       </c>
       <c r="B113" t="n">
-        <v>78920</v>
+        <v>57080</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Grycksheden, Dlr</t>
+          <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>386364</v>
+        <v>386516</v>
       </c>
       <c r="R113" t="n">
-        <v>6758576</v>
+        <v>6758592</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12439,9 +12444,19 @@
           <t>2026-03-04</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12456,22 +12471,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Moa Björnberg dillner</t>
+          <t>Philipp Weiss, Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131448308</v>
+        <v>131440224</v>
       </c>
       <c r="B114" t="n">
-        <v>79873</v>
+        <v>78920</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12479,37 +12494,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gryckheden, Dlr</t>
+          <t>Grycksheden, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>386413</v>
+        <v>386364</v>
       </c>
       <c r="R114" t="n">
-        <v>6758591</v>
+        <v>6758576</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12536,19 +12551,9 @@
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>12:21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12563,22 +12568,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg dillner</t>
+          <t>Moa Björnberg dillner</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131448335</v>
+        <v>131448308</v>
       </c>
       <c r="B115" t="n">
-        <v>79254</v>
+        <v>79873</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12586,21 +12591,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12610,10 +12615,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>386526</v>
+        <v>386413</v>
       </c>
       <c r="R115" t="n">
-        <v>6758655</v>
+        <v>6758591</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12645,7 +12650,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12655,7 +12660,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12682,50 +12687,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131448287</v>
+        <v>131448335</v>
       </c>
       <c r="B116" t="n">
-        <v>57080</v>
+        <v>79254</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Gryckheden, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>386516</v>
+        <v>386526</v>
       </c>
       <c r="R116" t="n">
-        <v>6758592</v>
+        <v>6758655</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 6176-2026 artfynd.xlsx
+++ b/artfynd/A 6176-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY161"/>
+  <dimension ref="A1:AZ161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440224</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440225</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448259</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448286</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448291</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448293</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448325</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448339</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448344</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448354</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448363</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448374</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448379</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448387</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2364,6 +2444,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448391</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2471,6 +2556,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448394</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448395</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448402</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448405</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,6 +3004,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448272</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2996,6 +3106,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440215</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3093,6 +3208,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440216</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3190,6 +3310,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440217</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3287,6 +3412,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440219</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3384,6 +3514,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440220</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3481,6 +3616,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440221</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3588,6 +3728,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448265</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3695,6 +3840,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448266</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3802,6 +3952,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448267</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3909,6 +4064,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448274</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4016,6 +4176,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448277</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4123,6 +4288,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448279</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4230,6 +4400,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448284</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4337,6 +4512,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448285</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4444,6 +4624,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448289</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4551,6 +4736,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448292</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4658,6 +4848,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448295</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4765,6 +4960,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448297</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4872,6 +5072,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448299</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4979,6 +5184,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448301</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5086,6 +5296,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448304</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5193,6 +5408,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448306</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5300,6 +5520,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448307</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5407,6 +5632,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448315</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5514,6 +5744,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448318</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5621,6 +5856,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448322</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5728,6 +5968,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448323</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5835,6 +6080,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448324</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5942,6 +6192,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448327</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6049,6 +6304,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448328</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6156,6 +6416,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448329</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6263,6 +6528,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448330</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6370,6 +6640,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448334</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6477,6 +6752,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448335</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6584,6 +6864,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448337</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6691,6 +6976,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448341</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6798,6 +7088,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448343</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6905,6 +7200,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448345</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7012,6 +7312,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448347</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7119,6 +7424,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448349</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7226,6 +7536,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448351</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7333,6 +7648,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448353</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7440,6 +7760,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448355</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7547,6 +7872,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448357</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7654,6 +7984,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448361</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7761,6 +8096,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448362</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7868,6 +8208,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448365</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7975,6 +8320,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448366</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8082,6 +8432,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448368</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8189,6 +8544,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448369</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8296,6 +8656,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448372</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8403,6 +8768,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448375</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8510,6 +8880,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448376</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8617,6 +8992,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448380</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8724,6 +9104,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448381</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8831,6 +9216,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448382</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8938,6 +9328,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448384</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9045,6 +9440,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448386</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9152,6 +9552,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448396</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9259,6 +9664,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448397</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9366,6 +9776,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448399</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9473,6 +9888,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448401</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9580,6 +10000,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448403</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9687,6 +10112,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448404</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9794,6 +10224,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448408</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9901,6 +10336,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448410</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9999,6 +10439,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440197</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10096,6 +10541,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440204</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10193,6 +10643,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440205</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10290,6 +10745,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440206</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10397,6 +10857,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448316</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10504,6 +10969,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448356</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10611,6 +11081,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448360</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10718,6 +11193,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448367</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10825,6 +11305,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448383</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10932,6 +11417,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448388</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11029,6 +11519,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440210</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11136,6 +11631,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448281</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11243,6 +11743,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448378</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11341,6 +11846,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440152</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11438,6 +11948,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440166</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11535,6 +12050,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440167</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11632,6 +12152,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440168</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11729,6 +12254,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440169</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11826,6 +12356,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440170</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11923,6 +12458,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440171</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12020,6 +12560,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440172</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12127,6 +12672,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448260</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12234,6 +12784,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448275</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12341,6 +12896,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448282</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12448,6 +13008,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448308</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12555,6 +13120,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448312</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12662,6 +13232,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448317</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12769,6 +13344,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448332</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12876,6 +13456,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448333</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12983,6 +13568,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448342</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13090,6 +13680,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448346</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13197,6 +13792,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448352</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13304,6 +13904,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448359</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13411,6 +14016,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448377</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13518,6 +14128,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448389</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13625,6 +14240,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448392</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13732,6 +14352,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448406</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13837,6 +14462,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440179</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13942,6 +14572,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440180</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14047,6 +14682,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440181</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14152,6 +14792,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440182</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14257,6 +14902,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440183</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14362,6 +15012,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440184</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14467,6 +15122,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440185</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14572,6 +15232,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440186</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14677,6 +15342,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440187</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14782,6 +15452,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440188</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14887,6 +15562,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440189</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14992,6 +15672,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440190</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15097,6 +15782,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440191</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15202,6 +15892,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440192</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15314,6 +16009,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448268</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15426,6 +16126,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448269</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15538,6 +16243,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448270</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15650,6 +16360,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448271</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15762,6 +16477,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448283</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15874,6 +16594,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448287</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15986,6 +16711,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448303</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16098,6 +16828,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448311</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16210,6 +16945,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448314</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16322,6 +17062,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448319</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16434,6 +17179,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448320</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16546,6 +17296,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448321</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16658,6 +17413,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448331</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16770,6 +17530,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448364</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16877,6 +17642,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448280</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16984,6 +17754,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448338</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17091,6 +17866,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448350</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17198,6 +17978,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448393</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17305,6 +18090,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448370</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17402,6 +18192,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440193</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17499,6 +18294,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131440194</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17606,8 +18406,175 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131448294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>